--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/HR/dT3/RANDOMSEARCH_DETAILS_dT3.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/HR/dT3/RANDOMSEARCH_DETAILS_dT3.xlsx
@@ -413,9 +413,5524 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8796</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.9323</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35.4762</v>
+      </c>
+      <c r="H2" t="n">
+        <v>56.8991</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9547</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.8786</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24.5517</v>
+      </c>
+      <c r="H3" t="n">
+        <v>55.2337</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9669</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.9493</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21.4985</v>
+      </c>
+      <c r="H4" t="n">
+        <v>57.4142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8633</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.0536</v>
+      </c>
+      <c r="G5" t="n">
+        <v>36.3431</v>
+      </c>
+      <c r="H5" t="n">
+        <v>60.4865</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.0894</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40.4109</v>
+      </c>
+      <c r="H6" t="n">
+        <v>61.505</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8959</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.0684</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33.9566</v>
+      </c>
+      <c r="H7" t="n">
+        <v>60.9111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.0659</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39.0568</v>
+      </c>
+      <c r="H8" t="n">
+        <v>60.8396</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9756</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.8265</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19.6832</v>
+      </c>
+      <c r="H9" t="n">
+        <v>53.5721</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8149</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.0674</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.3214</v>
+      </c>
+      <c r="H10" t="n">
+        <v>60.8819</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8199</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.0775</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39.2427</v>
+      </c>
+      <c r="H11" t="n">
+        <v>61.1694</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.8175</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="G12" t="n">
+        <v>39.1186</v>
+      </c>
+      <c r="H12" t="n">
+        <v>61.0978</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.0722</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.2888</v>
+      </c>
+      <c r="H13" t="n">
+        <v>61.0184</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8198</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.0769</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39.1912</v>
+      </c>
+      <c r="H14" t="n">
+        <v>61.1516</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8188</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.0757</v>
+      </c>
+      <c r="G15" t="n">
+        <v>38.9814</v>
+      </c>
+      <c r="H15" t="n">
+        <v>61.1179</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.0727</v>
+      </c>
+      <c r="G16" t="n">
+        <v>37.5279</v>
+      </c>
+      <c r="H16" t="n">
+        <v>61.0325</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8161</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.0729</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.135</v>
+      </c>
+      <c r="H17" t="n">
+        <v>61.0367</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9071</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.8042</v>
+      </c>
+      <c r="G18" t="n">
+        <v>29.7854</v>
+      </c>
+      <c r="H18" t="n">
+        <v>52.846</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.8651</v>
+      </c>
+      <c r="G19" t="n">
+        <v>23.647</v>
+      </c>
+      <c r="H19" t="n">
+        <v>54.8078</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8832</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.8773</v>
+      </c>
+      <c r="G20" t="n">
+        <v>33.5747</v>
+      </c>
+      <c r="H20" t="n">
+        <v>55.194</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8828</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.8585</v>
+      </c>
+      <c r="G21" t="n">
+        <v>33.1674</v>
+      </c>
+      <c r="H21" t="n">
+        <v>54.6007</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.8528</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.8458</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.5549</v>
+      </c>
+      <c r="H22" t="n">
+        <v>54.1956</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8847</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.8572</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33.1686</v>
+      </c>
+      <c r="H23" t="n">
+        <v>54.5593</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.8654</v>
+      </c>
+      <c r="G24" t="n">
+        <v>28.1391</v>
+      </c>
+      <c r="H24" t="n">
+        <v>54.8178</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8287</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.8682</v>
+      </c>
+      <c r="G25" t="n">
+        <v>37.3012</v>
+      </c>
+      <c r="H25" t="n">
+        <v>54.9057</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9788</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.8616</v>
+      </c>
+      <c r="G26" t="n">
+        <v>21.1794</v>
+      </c>
+      <c r="H26" t="n">
+        <v>54.6972</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9087</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.8439</v>
+      </c>
+      <c r="G27" t="n">
+        <v>29.9331</v>
+      </c>
+      <c r="H27" t="n">
+        <v>54.1328</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9005</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G28" t="n">
+        <v>33.0441</v>
+      </c>
+      <c r="H28" t="n">
+        <v>54.3301</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9112</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.8607</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29.9467</v>
+      </c>
+      <c r="H29" t="n">
+        <v>54.6681</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8841</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.8563</v>
+      </c>
+      <c r="G30" t="n">
+        <v>33.1773</v>
+      </c>
+      <c r="H30" t="n">
+        <v>54.5305</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8768</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.8618</v>
+      </c>
+      <c r="G31" t="n">
+        <v>33.6892</v>
+      </c>
+      <c r="H31" t="n">
+        <v>54.7033</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8887</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.8446</v>
+      </c>
+      <c r="G32" t="n">
+        <v>31.0639</v>
+      </c>
+      <c r="H32" t="n">
+        <v>54.1555</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8831</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.8511</v>
+      </c>
+      <c r="G33" t="n">
+        <v>32.7892</v>
+      </c>
+      <c r="H33" t="n">
+        <v>54.3635</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9339</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.8207</v>
+      </c>
+      <c r="G34" t="n">
+        <v>27.4587</v>
+      </c>
+      <c r="H34" t="n">
+        <v>53.3856</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.8497</v>
+      </c>
+      <c r="G35" t="n">
+        <v>32.7759</v>
+      </c>
+      <c r="H35" t="n">
+        <v>54.3178</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9098000000000001</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.8336</v>
+      </c>
+      <c r="G36" t="n">
+        <v>29.2226</v>
+      </c>
+      <c r="H36" t="n">
+        <v>53.8036</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9287</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.8442</v>
+      </c>
+      <c r="G37" t="n">
+        <v>28.1082</v>
+      </c>
+      <c r="H37" t="n">
+        <v>54.1425</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.8758</v>
+      </c>
+      <c r="G38" t="n">
+        <v>36.9384</v>
+      </c>
+      <c r="H38" t="n">
+        <v>55.1483</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.8858</v>
+      </c>
+      <c r="G39" t="n">
+        <v>33.6056</v>
+      </c>
+      <c r="H39" t="n">
+        <v>55.4598</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8454</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.8785</v>
+      </c>
+      <c r="G40" t="n">
+        <v>37.1993</v>
+      </c>
+      <c r="H40" t="n">
+        <v>55.2322</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.8182</v>
+      </c>
+      <c r="G41" t="n">
+        <v>27.5408</v>
+      </c>
+      <c r="H41" t="n">
+        <v>53.3038</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8921</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.8487</v>
+      </c>
+      <c r="G42" t="n">
+        <v>32.7912</v>
+      </c>
+      <c r="H42" t="n">
+        <v>54.2887</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9097</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.8338</v>
+      </c>
+      <c r="G43" t="n">
+        <v>29.2409</v>
+      </c>
+      <c r="H43" t="n">
+        <v>53.8084</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.8466</v>
+      </c>
+      <c r="G44" t="n">
+        <v>28.1432</v>
+      </c>
+      <c r="H44" t="n">
+        <v>54.2186</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.8642</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.8847</v>
+      </c>
+      <c r="G45" t="n">
+        <v>36.9499</v>
+      </c>
+      <c r="H45" t="n">
+        <v>55.4276</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.8849</v>
+      </c>
+      <c r="G46" t="n">
+        <v>26.6641</v>
+      </c>
+      <c r="H46" t="n">
+        <v>55.4314</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.8448</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.8808</v>
+      </c>
+      <c r="G47" t="n">
+        <v>37.2015</v>
+      </c>
+      <c r="H47" t="n">
+        <v>55.3045</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9074</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.8175</v>
+      </c>
+      <c r="G48" t="n">
+        <v>29.4743</v>
+      </c>
+      <c r="H48" t="n">
+        <v>53.2813</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9029</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.8506</v>
+      </c>
+      <c r="G49" t="n">
+        <v>29.8439</v>
+      </c>
+      <c r="H49" t="n">
+        <v>54.3481</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.9229</v>
+      </c>
+      <c r="G50" t="n">
+        <v>36.923</v>
+      </c>
+      <c r="H50" t="n">
+        <v>56.6097</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8509</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.9091</v>
+      </c>
+      <c r="G51" t="n">
+        <v>35.9535</v>
+      </c>
+      <c r="H51" t="n">
+        <v>56.1846</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8648</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.8844</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.424</v>
+      </c>
+      <c r="H52" t="n">
+        <v>55.4178</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.8791</v>
+      </c>
+      <c r="G53" t="n">
+        <v>36.8625</v>
+      </c>
+      <c r="H53" t="n">
+        <v>55.2499</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.8764</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.8405</v>
+      </c>
+      <c r="G54" t="n">
+        <v>33.1199</v>
+      </c>
+      <c r="H54" t="n">
+        <v>54.0232</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8918</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.9625</v>
+      </c>
+      <c r="G55" t="n">
+        <v>31.3067</v>
+      </c>
+      <c r="H55" t="n">
+        <v>57.8134</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.8825</v>
+      </c>
+      <c r="G56" t="n">
+        <v>26.1901</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55.3578</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.8765</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35.9306</v>
+      </c>
+      <c r="H57" t="n">
+        <v>55.1697</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8306</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.093</v>
+      </c>
+      <c r="G58" t="n">
+        <v>40.322</v>
+      </c>
+      <c r="H58" t="n">
+        <v>61.6057</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.8132</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.0966</v>
+      </c>
+      <c r="G59" t="n">
+        <v>41.7062</v>
+      </c>
+      <c r="H59" t="n">
+        <v>61.7077</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8153</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.0987</v>
+      </c>
+      <c r="G60" t="n">
+        <v>41.7097</v>
+      </c>
+      <c r="H60" t="n">
+        <v>61.7676</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8073</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.1011</v>
+      </c>
+      <c r="G61" t="n">
+        <v>41.9436</v>
+      </c>
+      <c r="H61" t="n">
+        <v>61.8357</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8728</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.9298</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.825</v>
+      </c>
+      <c r="H62" t="n">
+        <v>56.8217</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8759</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.9217</v>
+      </c>
+      <c r="G63" t="n">
+        <v>32.6652</v>
+      </c>
+      <c r="H63" t="n">
+        <v>56.5742</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8708</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.9843</v>
+      </c>
+      <c r="G64" t="n">
+        <v>33.6425</v>
+      </c>
+      <c r="H64" t="n">
+        <v>58.4633</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8773</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="G65" t="n">
+        <v>33.5492</v>
+      </c>
+      <c r="H65" t="n">
+        <v>58.006</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.9155</v>
+      </c>
+      <c r="G66" t="n">
+        <v>37.2874</v>
+      </c>
+      <c r="H66" t="n">
+        <v>56.3845</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.8878</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.8995</v>
+      </c>
+      <c r="G67" t="n">
+        <v>31.9637</v>
+      </c>
+      <c r="H67" t="n">
+        <v>55.8878</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.8784</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.9035</v>
+      </c>
+      <c r="G68" t="n">
+        <v>35.6411</v>
+      </c>
+      <c r="H68" t="n">
+        <v>56.0133</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8354</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.9712</v>
+      </c>
+      <c r="G69" t="n">
+        <v>36.5972</v>
+      </c>
+      <c r="H69" t="n">
+        <v>58.0726</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.9703</v>
+      </c>
+      <c r="G70" t="n">
+        <v>35.0963</v>
+      </c>
+      <c r="H70" t="n">
+        <v>58.0457</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8646</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.9536</v>
+      </c>
+      <c r="G71" t="n">
+        <v>33.8664</v>
+      </c>
+      <c r="H71" t="n">
+        <v>57.543</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.7889</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.9763</v>
+      </c>
+      <c r="G72" t="n">
+        <v>40.2994</v>
+      </c>
+      <c r="H72" t="n">
+        <v>58.2249</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.8569</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.9309</v>
+      </c>
+      <c r="G73" t="n">
+        <v>36.6617</v>
+      </c>
+      <c r="H73" t="n">
+        <v>56.8553</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.8635</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.9168</v>
+      </c>
+      <c r="G74" t="n">
+        <v>34.2777</v>
+      </c>
+      <c r="H74" t="n">
+        <v>56.4217</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.8366</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.0483</v>
+      </c>
+      <c r="G75" t="n">
+        <v>37.1537</v>
+      </c>
+      <c r="H75" t="n">
+        <v>60.3339</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8366</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.0483</v>
+      </c>
+      <c r="G76" t="n">
+        <v>37.1537</v>
+      </c>
+      <c r="H76" t="n">
+        <v>60.3339</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.0752</v>
+      </c>
+      <c r="G77" t="n">
+        <v>41.0568</v>
+      </c>
+      <c r="H77" t="n">
+        <v>61.1047</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8105</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.0753</v>
+      </c>
+      <c r="G78" t="n">
+        <v>41.4008</v>
+      </c>
+      <c r="H78" t="n">
+        <v>61.1064</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8094</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.0809</v>
+      </c>
+      <c r="G79" t="n">
+        <v>41.4587</v>
+      </c>
+      <c r="H79" t="n">
+        <v>61.2655</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8114</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.0737</v>
+      </c>
+      <c r="G80" t="n">
+        <v>41.3378</v>
+      </c>
+      <c r="H80" t="n">
+        <v>61.0606</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.9227</v>
+      </c>
+      <c r="G81" t="n">
+        <v>32.9225</v>
+      </c>
+      <c r="H81" t="n">
+        <v>56.6032</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.9367</v>
+      </c>
+      <c r="G82" t="n">
+        <v>21.8957</v>
+      </c>
+      <c r="H82" t="n">
+        <v>57.0335</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9066</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.0576</v>
+      </c>
+      <c r="G83" t="n">
+        <v>30.6794</v>
+      </c>
+      <c r="H83" t="n">
+        <v>60.6026</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9046999999999999</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.0532</v>
+      </c>
+      <c r="G84" t="n">
+        <v>30.8357</v>
+      </c>
+      <c r="H84" t="n">
+        <v>60.4755</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.0576</v>
+      </c>
+      <c r="G85" t="n">
+        <v>37.2952</v>
+      </c>
+      <c r="H85" t="n">
+        <v>60.6007</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9051</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.8403</v>
+      </c>
+      <c r="G86" t="n">
+        <v>30.382</v>
+      </c>
+      <c r="H86" t="n">
+        <v>54.0168</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.8988</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="G87" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="H87" t="n">
+        <v>54.7118</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.8971</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.9009</v>
+      </c>
+      <c r="G88" t="n">
+        <v>31.237</v>
+      </c>
+      <c r="H88" t="n">
+        <v>55.9321</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.9121</v>
+      </c>
+      <c r="G89" t="n">
+        <v>33.9542</v>
+      </c>
+      <c r="H89" t="n">
+        <v>56.2784</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.8339</v>
+      </c>
+      <c r="G90" t="n">
+        <v>29.2561</v>
+      </c>
+      <c r="H90" t="n">
+        <v>53.813</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.8464</v>
+      </c>
+      <c r="G91" t="n">
+        <v>28.1467</v>
+      </c>
+      <c r="H91" t="n">
+        <v>54.213</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.8971</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.9009</v>
+      </c>
+      <c r="G92" t="n">
+        <v>31.237</v>
+      </c>
+      <c r="H92" t="n">
+        <v>55.9321</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.8464</v>
+      </c>
+      <c r="G93" t="n">
+        <v>28.1467</v>
+      </c>
+      <c r="H93" t="n">
+        <v>54.213</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9669</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.9493</v>
+      </c>
+      <c r="G94" t="n">
+        <v>21.4985</v>
+      </c>
+      <c r="H94" t="n">
+        <v>57.4142</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.7904</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.1358</v>
+      </c>
+      <c r="G95" t="n">
+        <v>42.6939</v>
+      </c>
+      <c r="H95" t="n">
+        <v>62.8023</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8721</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.9393</v>
+      </c>
+      <c r="G96" t="n">
+        <v>35.2133</v>
+      </c>
+      <c r="H96" t="n">
+        <v>57.1113</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.9377</v>
+      </c>
+      <c r="G97" t="n">
+        <v>28.2502</v>
+      </c>
+      <c r="H97" t="n">
+        <v>57.0635</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9029</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.8257</v>
+      </c>
+      <c r="G98" t="n">
+        <v>29.9956</v>
+      </c>
+      <c r="H98" t="n">
+        <v>53.5479</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.8997000000000001</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.906</v>
+      </c>
+      <c r="G99" t="n">
+        <v>33.7179</v>
+      </c>
+      <c r="H99" t="n">
+        <v>56.0885</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9304</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.8897</v>
+      </c>
+      <c r="G100" t="n">
+        <v>30.1391</v>
+      </c>
+      <c r="H100" t="n">
+        <v>55.5828</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9274</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.8918</v>
+      </c>
+      <c r="G101" t="n">
+        <v>28.2514</v>
+      </c>
+      <c r="H101" t="n">
+        <v>55.6478</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.8894</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.9224</v>
+      </c>
+      <c r="G102" t="n">
+        <v>33.4419</v>
+      </c>
+      <c r="H102" t="n">
+        <v>56.596</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9014</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.8472</v>
+      </c>
+      <c r="G103" t="n">
+        <v>30.3509</v>
+      </c>
+      <c r="H103" t="n">
+        <v>54.2395</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.8951</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.8685</v>
+      </c>
+      <c r="G104" t="n">
+        <v>33.1695</v>
+      </c>
+      <c r="H104" t="n">
+        <v>54.9174</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.8667</v>
+      </c>
+      <c r="G105" t="n">
+        <v>30.2069</v>
+      </c>
+      <c r="H105" t="n">
+        <v>54.8595</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.8959</v>
+      </c>
+      <c r="G106" t="n">
+        <v>21.1915</v>
+      </c>
+      <c r="H106" t="n">
+        <v>55.7771</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.8959</v>
+      </c>
+      <c r="G107" t="n">
+        <v>21.1323</v>
+      </c>
+      <c r="H107" t="n">
+        <v>55.7752</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.8656</v>
+      </c>
+      <c r="G108" t="n">
+        <v>32.3814</v>
+      </c>
+      <c r="H108" t="n">
+        <v>54.8263</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9087</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.8292</v>
+      </c>
+      <c r="G109" t="n">
+        <v>29.3713</v>
+      </c>
+      <c r="H109" t="n">
+        <v>53.6593</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9039</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.8488</v>
+      </c>
+      <c r="G110" t="n">
+        <v>30.3073</v>
+      </c>
+      <c r="H110" t="n">
+        <v>54.2913</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.8772</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.8873</v>
+      </c>
+      <c r="G111" t="n">
+        <v>33.743</v>
+      </c>
+      <c r="H111" t="n">
+        <v>55.5075</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.8613</v>
+      </c>
+      <c r="G112" t="n">
+        <v>32.4659</v>
+      </c>
+      <c r="H112" t="n">
+        <v>54.688</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.8274</v>
+      </c>
+      <c r="G113" t="n">
+        <v>29.3003</v>
+      </c>
+      <c r="H113" t="n">
+        <v>53.6028</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9038</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.8579</v>
+      </c>
+      <c r="G114" t="n">
+        <v>30.3425</v>
+      </c>
+      <c r="H114" t="n">
+        <v>54.5797</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.8803</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.8905</v>
+      </c>
+      <c r="G115" t="n">
+        <v>33.5836</v>
+      </c>
+      <c r="H115" t="n">
+        <v>55.6074</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.8842</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.9099</v>
+      </c>
+      <c r="G116" t="n">
+        <v>32.3853</v>
+      </c>
+      <c r="H116" t="n">
+        <v>56.211</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.9727</v>
+      </c>
+      <c r="G117" t="n">
+        <v>33.6299</v>
+      </c>
+      <c r="H117" t="n">
+        <v>58.1183</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8667</v>
+      </c>
+      <c r="G118" t="n">
+        <v>30.2069</v>
+      </c>
+      <c r="H118" t="n">
+        <v>54.8595</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.8274</v>
+      </c>
+      <c r="G119" t="n">
+        <v>29.3003</v>
+      </c>
+      <c r="H119" t="n">
+        <v>53.6028</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.0192</v>
+      </c>
+      <c r="G120" t="n">
+        <v>35.968</v>
+      </c>
+      <c r="H120" t="n">
+        <v>59.4919</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.0192</v>
+      </c>
+      <c r="G121" t="n">
+        <v>35.968</v>
+      </c>
+      <c r="H121" t="n">
+        <v>59.4919</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8837</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.9379</v>
+      </c>
+      <c r="G122" t="n">
+        <v>34.4531</v>
+      </c>
+      <c r="H122" t="n">
+        <v>57.0691</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9096</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.8277</v>
+      </c>
+      <c r="G123" t="n">
+        <v>29.2973</v>
+      </c>
+      <c r="H123" t="n">
+        <v>53.6109</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.8924</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.8715</v>
+      </c>
+      <c r="G124" t="n">
+        <v>33.1045</v>
+      </c>
+      <c r="H124" t="n">
+        <v>55.0112</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>128</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9265</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.9433</v>
+      </c>
+      <c r="G125" t="n">
+        <v>28.7581</v>
+      </c>
+      <c r="H125" t="n">
+        <v>57.2323</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>129</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.8678</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.0881</v>
+      </c>
+      <c r="G126" t="n">
+        <v>36.0423</v>
+      </c>
+      <c r="H126" t="n">
+        <v>61.4689</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>130</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="G127" t="n">
+        <v>36.0802</v>
+      </c>
+      <c r="H127" t="n">
+        <v>58.4472</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>131</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0.8631</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.0869</v>
+      </c>
+      <c r="G128" t="n">
+        <v>36.5375</v>
+      </c>
+      <c r="H128" t="n">
+        <v>61.4356</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>132</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0.8565</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.0994</v>
+      </c>
+      <c r="G129" t="n">
+        <v>37.1822</v>
+      </c>
+      <c r="H129" t="n">
+        <v>61.786</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>133</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.8559</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2.0906</v>
+      </c>
+      <c r="G130" t="n">
+        <v>37.1213</v>
+      </c>
+      <c r="H130" t="n">
+        <v>61.5385</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>134</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0.9293</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2.0855</v>
+      </c>
+      <c r="G131" t="n">
+        <v>29.6303</v>
+      </c>
+      <c r="H131" t="n">
+        <v>61.396</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>135</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.0943</v>
+      </c>
+      <c r="G132" t="n">
+        <v>32.3592</v>
+      </c>
+      <c r="H132" t="n">
+        <v>61.6441</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>136</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0.8572</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.0882</v>
+      </c>
+      <c r="G133" t="n">
+        <v>36.8122</v>
+      </c>
+      <c r="H133" t="n">
+        <v>61.473</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>137</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0.8612</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.0963</v>
+      </c>
+      <c r="G134" t="n">
+        <v>36.5822</v>
+      </c>
+      <c r="H134" t="n">
+        <v>61.7003</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>138</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.0923</v>
+      </c>
+      <c r="G135" t="n">
+        <v>36.8706</v>
+      </c>
+      <c r="H135" t="n">
+        <v>61.5886</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>139</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0.9316</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.0866</v>
+      </c>
+      <c r="G136" t="n">
+        <v>29.4965</v>
+      </c>
+      <c r="H136" t="n">
+        <v>61.4252</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>140</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,2,11))</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0.9769</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.8855</v>
+      </c>
+      <c r="G137" t="n">
+        <v>21.0941</v>
+      </c>
+      <c r="H137" t="n">
+        <v>55.4506</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>141</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.8315</v>
+      </c>
+      <c r="G138" t="n">
+        <v>30.1262</v>
+      </c>
+      <c r="H138" t="n">
+        <v>53.7358</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>142</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0.8834</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.8963</v>
+      </c>
+      <c r="G139" t="n">
+        <v>34.0618</v>
+      </c>
+      <c r="H139" t="n">
+        <v>55.789</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>143</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0.9136</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="G140" t="n">
+        <v>28.8848</v>
+      </c>
+      <c r="H140" t="n">
+        <v>52.9029</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>144</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0.9056999999999999</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.8799</v>
+      </c>
+      <c r="G141" t="n">
+        <v>30.5956</v>
+      </c>
+      <c r="H141" t="n">
+        <v>55.2772</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>145</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0.9167</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8315</v>
+      </c>
+      <c r="G142" t="n">
+        <v>30.1262</v>
+      </c>
+      <c r="H142" t="n">
+        <v>53.7358</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>146</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,25))</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.8982</v>
+      </c>
+      <c r="G143" t="n">
+        <v>32.0823</v>
+      </c>
+      <c r="H143" t="n">
+        <v>55.8487</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>147</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0.8797</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.8916</v>
+      </c>
+      <c r="G144" t="n">
+        <v>34.1064</v>
+      </c>
+      <c r="H144" t="n">
+        <v>55.6438</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>148</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0.9056999999999999</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.8799</v>
+      </c>
+      <c r="G145" t="n">
+        <v>30.5956</v>
+      </c>
+      <c r="H145" t="n">
+        <v>55.2772</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>149</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.9869</v>
+      </c>
+      <c r="G146" t="n">
+        <v>35.6587</v>
+      </c>
+      <c r="H146" t="n">
+        <v>58.5413</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>150</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="G147" t="n">
+        <v>36.1187</v>
+      </c>
+      <c r="H147" t="n">
+        <v>58.8399</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>151</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0.8589</v>
+      </c>
+      <c r="F148" t="n">
+        <v>2.0002</v>
+      </c>
+      <c r="G148" t="n">
+        <v>35.8903</v>
+      </c>
+      <c r="H148" t="n">
+        <v>58.9326</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>152</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2.0035</v>
+      </c>
+      <c r="G149" t="n">
+        <v>35.8015</v>
+      </c>
+      <c r="H149" t="n">
+        <v>59.0313</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>153</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0.8588</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.9839</v>
+      </c>
+      <c r="G150" t="n">
+        <v>35.8139</v>
+      </c>
+      <c r="H150" t="n">
+        <v>58.4524</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>154</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0.8607</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1.9862</v>
+      </c>
+      <c r="G151" t="n">
+        <v>35.717</v>
+      </c>
+      <c r="H151" t="n">
+        <v>58.5201</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>155</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0.8609</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.9815</v>
+      </c>
+      <c r="G152" t="n">
+        <v>35.788</v>
+      </c>
+      <c r="H152" t="n">
+        <v>58.3806</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>156</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0.8643999999999999</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1.9859</v>
+      </c>
+      <c r="G153" t="n">
+        <v>35.5437</v>
+      </c>
+      <c r="H153" t="n">
+        <v>58.511</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>157</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.9822</v>
+      </c>
+      <c r="G154" t="n">
+        <v>35.5035</v>
+      </c>
+      <c r="H154" t="n">
+        <v>58.4002</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>158</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1.9078</v>
+      </c>
+      <c r="G155" t="n">
+        <v>31.9896</v>
+      </c>
+      <c r="H155" t="n">
+        <v>56.1471</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>159</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,25))</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1.9082</v>
+      </c>
+      <c r="G156" t="n">
+        <v>32.0706</v>
+      </c>
+      <c r="H156" t="n">
+        <v>56.1567</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>160</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0.8867</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1.8988</v>
+      </c>
+      <c r="G157" t="n">
+        <v>32.4796</v>
+      </c>
+      <c r="H157" t="n">
+        <v>55.8665</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>161</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.8754999999999999</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1.8904</v>
+      </c>
+      <c r="G158" t="n">
+        <v>35.0827</v>
+      </c>
+      <c r="H158" t="n">
+        <v>55.6053</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>162</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.8532</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2.0545</v>
+      </c>
+      <c r="G159" t="n">
+        <v>35.4186</v>
+      </c>
+      <c r="H159" t="n">
+        <v>60.5127</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>163</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1.9798</v>
+      </c>
+      <c r="G160" t="n">
+        <v>33.0023</v>
+      </c>
+      <c r="H160" t="n">
+        <v>58.3299</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>164</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1.9762</v>
+      </c>
+      <c r="G161" t="n">
+        <v>35.5064</v>
+      </c>
+      <c r="H161" t="n">
+        <v>58.2211</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>165</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2.0449</v>
+      </c>
+      <c r="G162" t="n">
+        <v>35.5736</v>
+      </c>
+      <c r="H162" t="n">
+        <v>60.2354</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>166</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0.8961</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1.9154</v>
+      </c>
+      <c r="G163" t="n">
+        <v>32.4985</v>
+      </c>
+      <c r="H163" t="n">
+        <v>56.3811</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>167</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0.9137999999999999</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1.8062</v>
+      </c>
+      <c r="G164" t="n">
+        <v>28.8625</v>
+      </c>
+      <c r="H164" t="n">
+        <v>52.9097</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>168</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0.9265</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.9433</v>
+      </c>
+      <c r="G165" t="n">
+        <v>28.7581</v>
+      </c>
+      <c r="H165" t="n">
+        <v>57.2323</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>169</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0.8058999999999999</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.1209</v>
+      </c>
+      <c r="G166" t="n">
+        <v>41.6109</v>
+      </c>
+      <c r="H166" t="n">
+        <v>62.3896</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>170</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0.9074</v>
+      </c>
+      <c r="F167" t="n">
+        <v>1.8617</v>
+      </c>
+      <c r="G167" t="n">
+        <v>30.3829</v>
+      </c>
+      <c r="H167" t="n">
+        <v>54.7004</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>171</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0.9137999999999999</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1.8126</v>
+      </c>
+      <c r="G168" t="n">
+        <v>28.9638</v>
+      </c>
+      <c r="H168" t="n">
+        <v>53.1201</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>172</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1.9122</v>
+      </c>
+      <c r="G169" t="n">
+        <v>25.457</v>
+      </c>
+      <c r="H169" t="n">
+        <v>56.2814</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>173</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0.8473000000000001</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1.9126</v>
+      </c>
+      <c r="G170" t="n">
+        <v>37.8024</v>
+      </c>
+      <c r="H170" t="n">
+        <v>56.2933</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>174</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="G171" t="n">
+        <v>29.6294</v>
+      </c>
+      <c r="H171" t="n">
+        <v>54.1693</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>175</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('sder',c(1,3,31)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.9419</v>
+      </c>
+      <c r="G172" t="n">
+        <v>28.8077</v>
+      </c>
+      <c r="H172" t="n">
+        <v>57.1891</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/HR/dT3/RANDOMSEARCH_DETAILS_dT3.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/HR/dT3/RANDOMSEARCH_DETAILS_dT3.xlsx
@@ -481,7 +481,7 @@
         <v>0.8796</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9323</v>
+        <v>0.0677</v>
       </c>
       <c r="G2" t="n">
         <v>35.4762</v>
@@ -513,7 +513,7 @@
         <v>0.9547</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8786</v>
+        <v>0.1214</v>
       </c>
       <c r="G3" t="n">
         <v>24.5517</v>
@@ -545,7 +545,7 @@
         <v>0.9669</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9493</v>
+        <v>0.0507</v>
       </c>
       <c r="G4" t="n">
         <v>21.4985</v>
@@ -577,7 +577,7 @@
         <v>0.8633</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0536</v>
+        <v>-0.0536</v>
       </c>
       <c r="G5" t="n">
         <v>36.3431</v>
@@ -609,7 +609,7 @@
         <v>0.8313</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0894</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>40.4109</v>
@@ -641,7 +641,7 @@
         <v>0.8959</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0684</v>
+        <v>-0.0684</v>
       </c>
       <c r="G7" t="n">
         <v>33.9566</v>
@@ -673,7 +673,7 @@
         <v>0.8182</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0659</v>
+        <v>-0.0659</v>
       </c>
       <c r="G8" t="n">
         <v>39.0568</v>
@@ -705,7 +705,7 @@
         <v>0.9756</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8265</v>
+        <v>0.1735</v>
       </c>
       <c r="G9" t="n">
         <v>19.6832</v>
@@ -737,7 +737,7 @@
         <v>0.8149</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0674</v>
+        <v>-0.0674</v>
       </c>
       <c r="G10" t="n">
         <v>39.3214</v>
@@ -769,7 +769,7 @@
         <v>0.8199</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0775</v>
+        <v>-0.0775</v>
       </c>
       <c r="G11" t="n">
         <v>39.2427</v>
@@ -801,7 +801,7 @@
         <v>0.8175</v>
       </c>
       <c r="F12" t="n">
-        <v>2.075</v>
+        <v>-0.075</v>
       </c>
       <c r="G12" t="n">
         <v>39.1186</v>
@@ -833,7 +833,7 @@
         <v>0.8145</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0722</v>
+        <v>-0.0722</v>
       </c>
       <c r="G13" t="n">
         <v>39.2888</v>
@@ -865,7 +865,7 @@
         <v>0.8198</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0769</v>
+        <v>-0.0769</v>
       </c>
       <c r="G14" t="n">
         <v>39.1912</v>
@@ -897,7 +897,7 @@
         <v>0.8188</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0757</v>
+        <v>-0.0757</v>
       </c>
       <c r="G15" t="n">
         <v>38.9814</v>
@@ -929,7 +929,7 @@
         <v>0.843</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0727</v>
+        <v>-0.0727</v>
       </c>
       <c r="G16" t="n">
         <v>37.5279</v>
@@ -961,7 +961,7 @@
         <v>0.8161</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0729</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>39.135</v>
@@ -993,7 +993,7 @@
         <v>0.9071</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8042</v>
+        <v>0.1958</v>
       </c>
       <c r="G18" t="n">
         <v>29.7854</v>
@@ -1025,7 +1025,7 @@
         <v>0.965</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8651</v>
+        <v>0.1349</v>
       </c>
       <c r="G19" t="n">
         <v>23.647</v>
@@ -1057,7 +1057,7 @@
         <v>0.8832</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8773</v>
+        <v>0.1227</v>
       </c>
       <c r="G20" t="n">
         <v>33.5747</v>
@@ -1089,7 +1089,7 @@
         <v>0.8828</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8585</v>
+        <v>0.1415</v>
       </c>
       <c r="G21" t="n">
         <v>33.1674</v>
@@ -1121,7 +1121,7 @@
         <v>0.8528</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8458</v>
+        <v>0.1542</v>
       </c>
       <c r="G22" t="n">
         <v>35.5549</v>
@@ -1153,7 +1153,7 @@
         <v>0.8847</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8572</v>
+        <v>0.1428</v>
       </c>
       <c r="G23" t="n">
         <v>33.1686</v>
@@ -1185,7 +1185,7 @@
         <v>0.924</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8654</v>
+        <v>0.1346</v>
       </c>
       <c r="G24" t="n">
         <v>28.1391</v>
@@ -1217,7 +1217,7 @@
         <v>0.8287</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8682</v>
+        <v>0.1318</v>
       </c>
       <c r="G25" t="n">
         <v>37.3012</v>
@@ -1249,7 +1249,7 @@
         <v>0.9788</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8616</v>
+        <v>0.1384</v>
       </c>
       <c r="G26" t="n">
         <v>21.1794</v>
@@ -1281,7 +1281,7 @@
         <v>0.9087</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8439</v>
+        <v>0.1561</v>
       </c>
       <c r="G27" t="n">
         <v>29.9331</v>
@@ -1313,7 +1313,7 @@
         <v>0.9005</v>
       </c>
       <c r="F28" t="n">
-        <v>1.85</v>
+        <v>0.15</v>
       </c>
       <c r="G28" t="n">
         <v>33.0441</v>
@@ -1345,7 +1345,7 @@
         <v>0.9112</v>
       </c>
       <c r="F29" t="n">
-        <v>1.8607</v>
+        <v>0.1393</v>
       </c>
       <c r="G29" t="n">
         <v>29.9467</v>
@@ -1377,7 +1377,7 @@
         <v>0.8841</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8563</v>
+        <v>0.1437</v>
       </c>
       <c r="G30" t="n">
         <v>33.1773</v>
@@ -1409,7 +1409,7 @@
         <v>0.8768</v>
       </c>
       <c r="F31" t="n">
-        <v>1.8618</v>
+        <v>0.1382</v>
       </c>
       <c r="G31" t="n">
         <v>33.6892</v>
@@ -1441,7 +1441,7 @@
         <v>0.8887</v>
       </c>
       <c r="F32" t="n">
-        <v>1.8446</v>
+        <v>0.1554</v>
       </c>
       <c r="G32" t="n">
         <v>31.0639</v>
@@ -1473,7 +1473,7 @@
         <v>0.8831</v>
       </c>
       <c r="F33" t="n">
-        <v>1.8511</v>
+        <v>0.1489</v>
       </c>
       <c r="G33" t="n">
         <v>32.7892</v>
@@ -1505,7 +1505,7 @@
         <v>0.9339</v>
       </c>
       <c r="F34" t="n">
-        <v>1.8207</v>
+        <v>0.1793</v>
       </c>
       <c r="G34" t="n">
         <v>27.4587</v>
@@ -1537,7 +1537,7 @@
         <v>0.8925</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8497</v>
+        <v>0.1503</v>
       </c>
       <c r="G35" t="n">
         <v>32.7759</v>
@@ -1569,7 +1569,7 @@
         <v>0.9098000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>1.8336</v>
+        <v>0.1664</v>
       </c>
       <c r="G36" t="n">
         <v>29.2226</v>
@@ -1601,7 +1601,7 @@
         <v>0.9287</v>
       </c>
       <c r="F37" t="n">
-        <v>1.8442</v>
+        <v>0.1558</v>
       </c>
       <c r="G37" t="n">
         <v>28.1082</v>
@@ -1633,7 +1633,7 @@
         <v>0.8636</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8758</v>
+        <v>0.1242</v>
       </c>
       <c r="G38" t="n">
         <v>36.9384</v>
@@ -1665,7 +1665,7 @@
         <v>0.8766</v>
       </c>
       <c r="F39" t="n">
-        <v>1.8858</v>
+        <v>0.1142</v>
       </c>
       <c r="G39" t="n">
         <v>33.6056</v>
@@ -1697,7 +1697,7 @@
         <v>0.8454</v>
       </c>
       <c r="F40" t="n">
-        <v>1.8785</v>
+        <v>0.1215</v>
       </c>
       <c r="G40" t="n">
         <v>37.1993</v>
@@ -1729,7 +1729,7 @@
         <v>0.9332</v>
       </c>
       <c r="F41" t="n">
-        <v>1.8182</v>
+        <v>0.1818</v>
       </c>
       <c r="G41" t="n">
         <v>27.5408</v>
@@ -1761,7 +1761,7 @@
         <v>0.8921</v>
       </c>
       <c r="F42" t="n">
-        <v>1.8487</v>
+        <v>0.1513</v>
       </c>
       <c r="G42" t="n">
         <v>32.7912</v>
@@ -1793,7 +1793,7 @@
         <v>0.9097</v>
       </c>
       <c r="F43" t="n">
-        <v>1.8338</v>
+        <v>0.1662</v>
       </c>
       <c r="G43" t="n">
         <v>29.2409</v>
@@ -1825,7 +1825,7 @@
         <v>0.9282</v>
       </c>
       <c r="F44" t="n">
-        <v>1.8466</v>
+        <v>0.1534</v>
       </c>
       <c r="G44" t="n">
         <v>28.1432</v>
@@ -1857,7 +1857,7 @@
         <v>0.8642</v>
       </c>
       <c r="F45" t="n">
-        <v>1.8847</v>
+        <v>0.1153</v>
       </c>
       <c r="G45" t="n">
         <v>36.9499</v>
@@ -1889,7 +1889,7 @@
         <v>0.9429</v>
       </c>
       <c r="F46" t="n">
-        <v>1.8849</v>
+        <v>0.1151</v>
       </c>
       <c r="G46" t="n">
         <v>26.6641</v>
@@ -1921,7 +1921,7 @@
         <v>0.8448</v>
       </c>
       <c r="F47" t="n">
-        <v>1.8808</v>
+        <v>0.1192</v>
       </c>
       <c r="G47" t="n">
         <v>37.2015</v>
@@ -1953,7 +1953,7 @@
         <v>0.9074</v>
       </c>
       <c r="F48" t="n">
-        <v>1.8175</v>
+        <v>0.1825</v>
       </c>
       <c r="G48" t="n">
         <v>29.4743</v>
@@ -1985,7 +1985,7 @@
         <v>0.9029</v>
       </c>
       <c r="F49" t="n">
-        <v>1.8506</v>
+        <v>0.1494</v>
       </c>
       <c r="G49" t="n">
         <v>29.8439</v>
@@ -2017,7 +2017,7 @@
         <v>0.8555</v>
       </c>
       <c r="F50" t="n">
-        <v>1.9229</v>
+        <v>0.0771</v>
       </c>
       <c r="G50" t="n">
         <v>36.923</v>
@@ -2049,7 +2049,7 @@
         <v>0.8509</v>
       </c>
       <c r="F51" t="n">
-        <v>1.9091</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G51" t="n">
         <v>35.9535</v>
@@ -2081,7 +2081,7 @@
         <v>0.8648</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8844</v>
+        <v>0.1156</v>
       </c>
       <c r="G52" t="n">
         <v>34.424</v>
@@ -2113,7 +2113,7 @@
         <v>0.8476</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8791</v>
+        <v>0.1209</v>
       </c>
       <c r="G53" t="n">
         <v>36.8625</v>
@@ -2145,7 +2145,7 @@
         <v>0.8764</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8405</v>
+        <v>0.1595</v>
       </c>
       <c r="G54" t="n">
         <v>33.1199</v>
@@ -2177,7 +2177,7 @@
         <v>0.8918</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9625</v>
+        <v>0.0375</v>
       </c>
       <c r="G55" t="n">
         <v>31.3067</v>
@@ -2209,7 +2209,7 @@
         <v>0.944</v>
       </c>
       <c r="F56" t="n">
-        <v>1.8825</v>
+        <v>0.1175</v>
       </c>
       <c r="G56" t="n">
         <v>26.1901</v>
@@ -2241,7 +2241,7 @@
         <v>0.8584000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>1.8765</v>
+        <v>0.1235</v>
       </c>
       <c r="G57" t="n">
         <v>35.9306</v>
@@ -2273,7 +2273,7 @@
         <v>0.8306</v>
       </c>
       <c r="F58" t="n">
-        <v>2.093</v>
+        <v>-0.093</v>
       </c>
       <c r="G58" t="n">
         <v>40.322</v>
@@ -2305,7 +2305,7 @@
         <v>0.8132</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0966</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="G59" t="n">
         <v>41.7062</v>
@@ -2337,7 +2337,7 @@
         <v>0.8153</v>
       </c>
       <c r="F60" t="n">
-        <v>2.0987</v>
+        <v>-0.0987</v>
       </c>
       <c r="G60" t="n">
         <v>41.7097</v>
@@ -2369,7 +2369,7 @@
         <v>0.8073</v>
       </c>
       <c r="F61" t="n">
-        <v>2.1011</v>
+        <v>-0.1011</v>
       </c>
       <c r="G61" t="n">
         <v>41.9436</v>
@@ -2401,7 +2401,7 @@
         <v>0.8728</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9298</v>
+        <v>0.0702</v>
       </c>
       <c r="G62" t="n">
         <v>34.825</v>
@@ -2433,7 +2433,7 @@
         <v>0.8759</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9217</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>32.6652</v>
@@ -2465,7 +2465,7 @@
         <v>0.8708</v>
       </c>
       <c r="F64" t="n">
-        <v>1.9843</v>
+        <v>0.0157</v>
       </c>
       <c r="G64" t="n">
         <v>33.6425</v>
@@ -2497,7 +2497,7 @@
         <v>0.8773</v>
       </c>
       <c r="F65" t="n">
-        <v>1.969</v>
+        <v>0.031</v>
       </c>
       <c r="G65" t="n">
         <v>33.5492</v>
@@ -2529,7 +2529,7 @@
         <v>0.8512999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>1.9155</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="G66" t="n">
         <v>37.2874</v>
@@ -2561,7 +2561,7 @@
         <v>0.8878</v>
       </c>
       <c r="F67" t="n">
-        <v>1.8995</v>
+        <v>0.1005</v>
       </c>
       <c r="G67" t="n">
         <v>31.9637</v>
@@ -2593,7 +2593,7 @@
         <v>0.8784</v>
       </c>
       <c r="F68" t="n">
-        <v>1.9035</v>
+        <v>0.0965</v>
       </c>
       <c r="G68" t="n">
         <v>35.6411</v>
@@ -2625,7 +2625,7 @@
         <v>0.8354</v>
       </c>
       <c r="F69" t="n">
-        <v>1.9712</v>
+        <v>0.0288</v>
       </c>
       <c r="G69" t="n">
         <v>36.5972</v>
@@ -2657,7 +2657,7 @@
         <v>0.8476</v>
       </c>
       <c r="F70" t="n">
-        <v>1.9703</v>
+        <v>0.0297</v>
       </c>
       <c r="G70" t="n">
         <v>35.0963</v>
@@ -2689,7 +2689,7 @@
         <v>0.8646</v>
       </c>
       <c r="F71" t="n">
-        <v>1.9536</v>
+        <v>0.0464</v>
       </c>
       <c r="G71" t="n">
         <v>33.8664</v>
@@ -2721,7 +2721,7 @@
         <v>0.7889</v>
       </c>
       <c r="F72" t="n">
-        <v>1.9763</v>
+        <v>0.0237</v>
       </c>
       <c r="G72" t="n">
         <v>40.2994</v>
@@ -2753,7 +2753,7 @@
         <v>0.8569</v>
       </c>
       <c r="F73" t="n">
-        <v>1.9309</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G73" t="n">
         <v>36.6617</v>
@@ -2785,7 +2785,7 @@
         <v>0.8635</v>
       </c>
       <c r="F74" t="n">
-        <v>1.9168</v>
+        <v>0.0832</v>
       </c>
       <c r="G74" t="n">
         <v>34.2777</v>
@@ -2817,7 +2817,7 @@
         <v>0.8366</v>
       </c>
       <c r="F75" t="n">
-        <v>2.0483</v>
+        <v>-0.0483</v>
       </c>
       <c r="G75" t="n">
         <v>37.1537</v>
@@ -2849,7 +2849,7 @@
         <v>0.8366</v>
       </c>
       <c r="F76" t="n">
-        <v>2.0483</v>
+        <v>-0.0483</v>
       </c>
       <c r="G76" t="n">
         <v>37.1537</v>
@@ -2881,7 +2881,7 @@
         <v>0.8166</v>
       </c>
       <c r="F77" t="n">
-        <v>2.0752</v>
+        <v>-0.0752</v>
       </c>
       <c r="G77" t="n">
         <v>41.0568</v>
@@ -2913,7 +2913,7 @@
         <v>0.8105</v>
       </c>
       <c r="F78" t="n">
-        <v>2.0753</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="G78" t="n">
         <v>41.4008</v>
@@ -2945,7 +2945,7 @@
         <v>0.8094</v>
       </c>
       <c r="F79" t="n">
-        <v>2.0809</v>
+        <v>-0.0809</v>
       </c>
       <c r="G79" t="n">
         <v>41.4587</v>
@@ -2977,7 +2977,7 @@
         <v>0.8114</v>
       </c>
       <c r="F80" t="n">
-        <v>2.0737</v>
+        <v>-0.0737</v>
       </c>
       <c r="G80" t="n">
         <v>41.3378</v>
@@ -3009,7 +3009,7 @@
         <v>0.88</v>
       </c>
       <c r="F81" t="n">
-        <v>1.9227</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G81" t="n">
         <v>32.9225</v>
@@ -3041,7 +3041,7 @@
         <v>0.976</v>
       </c>
       <c r="F82" t="n">
-        <v>1.9367</v>
+        <v>0.0633</v>
       </c>
       <c r="G82" t="n">
         <v>21.8957</v>
@@ -3073,7 +3073,7 @@
         <v>0.9066</v>
       </c>
       <c r="F83" t="n">
-        <v>2.0576</v>
+        <v>-0.0576</v>
       </c>
       <c r="G83" t="n">
         <v>30.6794</v>
@@ -3105,7 +3105,7 @@
         <v>0.9046999999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>2.0532</v>
+        <v>-0.0532</v>
       </c>
       <c r="G84" t="n">
         <v>30.8357</v>
@@ -3137,7 +3137,7 @@
         <v>0.835</v>
       </c>
       <c r="F85" t="n">
-        <v>2.0576</v>
+        <v>-0.0576</v>
       </c>
       <c r="G85" t="n">
         <v>37.2952</v>
@@ -3169,7 +3169,7 @@
         <v>0.9051</v>
       </c>
       <c r="F86" t="n">
-        <v>1.8403</v>
+        <v>0.1597</v>
       </c>
       <c r="G86" t="n">
         <v>30.382</v>
@@ -3201,7 +3201,7 @@
         <v>0.8988</v>
       </c>
       <c r="F87" t="n">
-        <v>1.862</v>
+        <v>0.138</v>
       </c>
       <c r="G87" t="n">
         <v>33.03</v>
@@ -3233,7 +3233,7 @@
         <v>0.8971</v>
       </c>
       <c r="F88" t="n">
-        <v>1.9009</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G88" t="n">
         <v>31.237</v>
@@ -3265,7 +3265,7 @@
         <v>0.8904</v>
       </c>
       <c r="F89" t="n">
-        <v>1.9121</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G89" t="n">
         <v>33.9542</v>
@@ -3297,7 +3297,7 @@
         <v>0.9095</v>
       </c>
       <c r="F90" t="n">
-        <v>1.8339</v>
+        <v>0.1661</v>
       </c>
       <c r="G90" t="n">
         <v>29.2561</v>
@@ -3329,7 +3329,7 @@
         <v>0.9282</v>
       </c>
       <c r="F91" t="n">
-        <v>1.8464</v>
+        <v>0.1536</v>
       </c>
       <c r="G91" t="n">
         <v>28.1467</v>
@@ -3361,7 +3361,7 @@
         <v>0.8971</v>
       </c>
       <c r="F92" t="n">
-        <v>1.9009</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G92" t="n">
         <v>31.237</v>
@@ -3393,7 +3393,7 @@
         <v>0.9282</v>
       </c>
       <c r="F93" t="n">
-        <v>1.8464</v>
+        <v>0.1536</v>
       </c>
       <c r="G93" t="n">
         <v>28.1467</v>
@@ -3425,7 +3425,7 @@
         <v>0.9669</v>
       </c>
       <c r="F94" t="n">
-        <v>1.9493</v>
+        <v>0.0507</v>
       </c>
       <c r="G94" t="n">
         <v>21.4985</v>
@@ -3457,7 +3457,7 @@
         <v>0.7904</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1358</v>
+        <v>-0.1358</v>
       </c>
       <c r="G95" t="n">
         <v>42.6939</v>
@@ -3489,7 +3489,7 @@
         <v>0.8721</v>
       </c>
       <c r="F96" t="n">
-        <v>1.9393</v>
+        <v>0.0607</v>
       </c>
       <c r="G96" t="n">
         <v>35.2133</v>
@@ -3521,7 +3521,7 @@
         <v>0.917</v>
       </c>
       <c r="F97" t="n">
-        <v>1.9377</v>
+        <v>0.0623</v>
       </c>
       <c r="G97" t="n">
         <v>28.2502</v>
@@ -3553,7 +3553,7 @@
         <v>0.9029</v>
       </c>
       <c r="F98" t="n">
-        <v>1.8257</v>
+        <v>0.1743</v>
       </c>
       <c r="G98" t="n">
         <v>29.9956</v>
@@ -3585,7 +3585,7 @@
         <v>0.8997000000000001</v>
       </c>
       <c r="F99" t="n">
-        <v>1.906</v>
+        <v>0.094</v>
       </c>
       <c r="G99" t="n">
         <v>33.7179</v>
@@ -3617,7 +3617,7 @@
         <v>0.9304</v>
       </c>
       <c r="F100" t="n">
-        <v>1.8897</v>
+        <v>0.1103</v>
       </c>
       <c r="G100" t="n">
         <v>30.1391</v>
@@ -3649,7 +3649,7 @@
         <v>0.9274</v>
       </c>
       <c r="F101" t="n">
-        <v>1.8918</v>
+        <v>0.1082</v>
       </c>
       <c r="G101" t="n">
         <v>28.2514</v>
@@ -3681,7 +3681,7 @@
         <v>0.8894</v>
       </c>
       <c r="F102" t="n">
-        <v>1.9224</v>
+        <v>0.0776</v>
       </c>
       <c r="G102" t="n">
         <v>33.4419</v>
@@ -3713,7 +3713,7 @@
         <v>0.9014</v>
       </c>
       <c r="F103" t="n">
-        <v>1.8472</v>
+        <v>0.1528</v>
       </c>
       <c r="G103" t="n">
         <v>30.3509</v>
@@ -3745,7 +3745,7 @@
         <v>0.8951</v>
       </c>
       <c r="F104" t="n">
-        <v>1.8685</v>
+        <v>0.1315</v>
       </c>
       <c r="G104" t="n">
         <v>33.1695</v>
@@ -3777,7 +3777,7 @@
         <v>0.9109</v>
       </c>
       <c r="F105" t="n">
-        <v>1.8667</v>
+        <v>0.1333</v>
       </c>
       <c r="G105" t="n">
         <v>30.2069</v>
@@ -3809,7 +3809,7 @@
         <v>0.9731</v>
       </c>
       <c r="F106" t="n">
-        <v>1.8959</v>
+        <v>0.1041</v>
       </c>
       <c r="G106" t="n">
         <v>21.1915</v>
@@ -3841,7 +3841,7 @@
         <v>0.9716</v>
       </c>
       <c r="F107" t="n">
-        <v>1.8959</v>
+        <v>0.1041</v>
       </c>
       <c r="G107" t="n">
         <v>21.1323</v>
@@ -3873,7 +3873,7 @@
         <v>0.893</v>
       </c>
       <c r="F108" t="n">
-        <v>1.8656</v>
+        <v>0.1344</v>
       </c>
       <c r="G108" t="n">
         <v>32.3814</v>
@@ -3905,7 +3905,7 @@
         <v>0.9087</v>
       </c>
       <c r="F109" t="n">
-        <v>1.8292</v>
+        <v>0.1708</v>
       </c>
       <c r="G109" t="n">
         <v>29.3713</v>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9039</v>
+        <v>0.9035</v>
       </c>
       <c r="F110" t="n">
-        <v>1.8488</v>
+        <v>0.1512</v>
       </c>
       <c r="G110" t="n">
-        <v>30.3073</v>
+        <v>30.3506</v>
       </c>
       <c r="H110" t="n">
         <v>54.2913</v>
@@ -3969,7 +3969,7 @@
         <v>0.8772</v>
       </c>
       <c r="F111" t="n">
-        <v>1.8873</v>
+        <v>0.1127</v>
       </c>
       <c r="G111" t="n">
         <v>33.743</v>
@@ -4001,7 +4001,7 @@
         <v>0.8923</v>
       </c>
       <c r="F112" t="n">
-        <v>1.8613</v>
+        <v>0.1387</v>
       </c>
       <c r="G112" t="n">
         <v>32.4659</v>
@@ -4033,7 +4033,7 @@
         <v>0.9095</v>
       </c>
       <c r="F113" t="n">
-        <v>1.8274</v>
+        <v>0.1726</v>
       </c>
       <c r="G113" t="n">
         <v>29.3003</v>
@@ -4058,17 +4058,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9038</v>
+        <v>0.9034</v>
       </c>
       <c r="F114" t="n">
-        <v>1.8579</v>
+        <v>0.1421</v>
       </c>
       <c r="G114" t="n">
-        <v>30.3425</v>
+        <v>30.386</v>
       </c>
       <c r="H114" t="n">
         <v>54.5797</v>
@@ -4097,7 +4097,7 @@
         <v>0.8803</v>
       </c>
       <c r="F115" t="n">
-        <v>1.8905</v>
+        <v>0.1095</v>
       </c>
       <c r="G115" t="n">
         <v>33.5836</v>
@@ -4129,7 +4129,7 @@
         <v>0.8842</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9099</v>
+        <v>0.0901</v>
       </c>
       <c r="G116" t="n">
         <v>32.3853</v>
@@ -4161,7 +4161,7 @@
         <v>0.8774</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9727</v>
+        <v>0.0273</v>
       </c>
       <c r="G117" t="n">
         <v>33.6299</v>
@@ -4193,7 +4193,7 @@
         <v>0.9109</v>
       </c>
       <c r="F118" t="n">
-        <v>1.8667</v>
+        <v>0.1333</v>
       </c>
       <c r="G118" t="n">
         <v>30.2069</v>
@@ -4225,7 +4225,7 @@
         <v>0.9095</v>
       </c>
       <c r="F119" t="n">
-        <v>1.8274</v>
+        <v>0.1726</v>
       </c>
       <c r="G119" t="n">
         <v>29.3003</v>
@@ -4257,7 +4257,7 @@
         <v>0.8611</v>
       </c>
       <c r="F120" t="n">
-        <v>2.0192</v>
+        <v>-0.0192</v>
       </c>
       <c r="G120" t="n">
         <v>35.968</v>
@@ -4289,7 +4289,7 @@
         <v>0.8611</v>
       </c>
       <c r="F121" t="n">
-        <v>2.0192</v>
+        <v>-0.0192</v>
       </c>
       <c r="G121" t="n">
         <v>35.968</v>
@@ -4321,7 +4321,7 @@
         <v>0.8837</v>
       </c>
       <c r="F122" t="n">
-        <v>1.9379</v>
+        <v>0.0621</v>
       </c>
       <c r="G122" t="n">
         <v>34.4531</v>
@@ -4353,7 +4353,7 @@
         <v>0.9096</v>
       </c>
       <c r="F123" t="n">
-        <v>1.8277</v>
+        <v>0.1723</v>
       </c>
       <c r="G123" t="n">
         <v>29.2973</v>
@@ -4378,17 +4378,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.8924</v>
+        <v>0.8925</v>
       </c>
       <c r="F124" t="n">
-        <v>1.8715</v>
+        <v>0.1285</v>
       </c>
       <c r="G124" t="n">
-        <v>33.1045</v>
+        <v>33.1135</v>
       </c>
       <c r="H124" t="n">
         <v>55.0112</v>
@@ -4417,7 +4417,7 @@
         <v>0.9265</v>
       </c>
       <c r="F125" t="n">
-        <v>1.9433</v>
+        <v>0.0567</v>
       </c>
       <c r="G125" t="n">
         <v>28.7581</v>
@@ -4449,7 +4449,7 @@
         <v>0.8678</v>
       </c>
       <c r="F126" t="n">
-        <v>2.0881</v>
+        <v>-0.0881</v>
       </c>
       <c r="G126" t="n">
         <v>36.0423</v>
@@ -4481,7 +4481,7 @@
         <v>0.8561</v>
       </c>
       <c r="F127" t="n">
-        <v>1.9838</v>
+        <v>0.0162</v>
       </c>
       <c r="G127" t="n">
         <v>36.0802</v>
@@ -4513,7 +4513,7 @@
         <v>0.8631</v>
       </c>
       <c r="F128" t="n">
-        <v>2.0869</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="G128" t="n">
         <v>36.5375</v>
@@ -4545,7 +4545,7 @@
         <v>0.8565</v>
       </c>
       <c r="F129" t="n">
-        <v>2.0994</v>
+        <v>-0.0994</v>
       </c>
       <c r="G129" t="n">
         <v>37.1822</v>
@@ -4577,7 +4577,7 @@
         <v>0.8559</v>
       </c>
       <c r="F130" t="n">
-        <v>2.0906</v>
+        <v>-0.0906</v>
       </c>
       <c r="G130" t="n">
         <v>37.1213</v>
@@ -4609,7 +4609,7 @@
         <v>0.9293</v>
       </c>
       <c r="F131" t="n">
-        <v>2.0855</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="G131" t="n">
         <v>29.6303</v>
@@ -4641,7 +4641,7 @@
         <v>0.9193</v>
       </c>
       <c r="F132" t="n">
-        <v>2.0943</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="G132" t="n">
         <v>32.3592</v>
@@ -4673,7 +4673,7 @@
         <v>0.8572</v>
       </c>
       <c r="F133" t="n">
-        <v>2.0882</v>
+        <v>-0.0882</v>
       </c>
       <c r="G133" t="n">
         <v>36.8122</v>
@@ -4705,7 +4705,7 @@
         <v>0.8612</v>
       </c>
       <c r="F134" t="n">
-        <v>2.0963</v>
+        <v>-0.0963</v>
       </c>
       <c r="G134" t="n">
         <v>36.5822</v>
@@ -4737,7 +4737,7 @@
         <v>0.8596</v>
       </c>
       <c r="F135" t="n">
-        <v>2.0923</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="G135" t="n">
         <v>36.8706</v>
@@ -4769,7 +4769,7 @@
         <v>0.9316</v>
       </c>
       <c r="F136" t="n">
-        <v>2.0866</v>
+        <v>-0.0866</v>
       </c>
       <c r="G136" t="n">
         <v>29.4965</v>
@@ -4801,7 +4801,7 @@
         <v>0.9769</v>
       </c>
       <c r="F137" t="n">
-        <v>1.8855</v>
+        <v>0.1145</v>
       </c>
       <c r="G137" t="n">
         <v>21.0941</v>
@@ -4833,7 +4833,7 @@
         <v>0.9167</v>
       </c>
       <c r="F138" t="n">
-        <v>1.8315</v>
+        <v>0.1685</v>
       </c>
       <c r="G138" t="n">
         <v>30.1262</v>
@@ -4865,7 +4865,7 @@
         <v>0.8834</v>
       </c>
       <c r="F139" t="n">
-        <v>1.8963</v>
+        <v>0.1037</v>
       </c>
       <c r="G139" t="n">
         <v>34.0618</v>
@@ -4897,7 +4897,7 @@
         <v>0.9136</v>
       </c>
       <c r="F140" t="n">
-        <v>1.806</v>
+        <v>0.194</v>
       </c>
       <c r="G140" t="n">
         <v>28.8848</v>
@@ -4929,7 +4929,7 @@
         <v>0.9056999999999999</v>
       </c>
       <c r="F141" t="n">
-        <v>1.8799</v>
+        <v>0.1201</v>
       </c>
       <c r="G141" t="n">
         <v>30.5956</v>
@@ -4961,7 +4961,7 @@
         <v>0.9167</v>
       </c>
       <c r="F142" t="n">
-        <v>1.8315</v>
+        <v>0.1685</v>
       </c>
       <c r="G142" t="n">
         <v>30.1262</v>
@@ -4993,7 +4993,7 @@
         <v>0.8885</v>
       </c>
       <c r="F143" t="n">
-        <v>1.8982</v>
+        <v>0.1018</v>
       </c>
       <c r="G143" t="n">
         <v>32.0823</v>
@@ -5018,17 +5018,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.8797</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="F144" t="n">
-        <v>1.8916</v>
+        <v>0.1084</v>
       </c>
       <c r="G144" t="n">
-        <v>34.1064</v>
+        <v>34.1263</v>
       </c>
       <c r="H144" t="n">
         <v>55.6438</v>
@@ -5057,7 +5057,7 @@
         <v>0.9056999999999999</v>
       </c>
       <c r="F145" t="n">
-        <v>1.8799</v>
+        <v>0.1201</v>
       </c>
       <c r="G145" t="n">
         <v>30.5956</v>
@@ -5089,7 +5089,7 @@
         <v>0.8611</v>
       </c>
       <c r="F146" t="n">
-        <v>1.9869</v>
+        <v>0.0131</v>
       </c>
       <c r="G146" t="n">
         <v>35.6587</v>
@@ -5121,7 +5121,7 @@
         <v>0.854</v>
       </c>
       <c r="F147" t="n">
-        <v>1.997</v>
+        <v>0.003</v>
       </c>
       <c r="G147" t="n">
         <v>36.1187</v>
@@ -5153,7 +5153,7 @@
         <v>0.8589</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0002</v>
+        <v>-0.0002</v>
       </c>
       <c r="G148" t="n">
         <v>35.8903</v>
@@ -5185,7 +5185,7 @@
         <v>0.861</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0035</v>
+        <v>-0.0035</v>
       </c>
       <c r="G149" t="n">
         <v>35.8015</v>
@@ -5217,7 +5217,7 @@
         <v>0.8588</v>
       </c>
       <c r="F150" t="n">
-        <v>1.9839</v>
+        <v>0.0161</v>
       </c>
       <c r="G150" t="n">
         <v>35.8139</v>
@@ -5249,7 +5249,7 @@
         <v>0.8607</v>
       </c>
       <c r="F151" t="n">
-        <v>1.9862</v>
+        <v>0.0138</v>
       </c>
       <c r="G151" t="n">
         <v>35.717</v>
@@ -5281,7 +5281,7 @@
         <v>0.8609</v>
       </c>
       <c r="F152" t="n">
-        <v>1.9815</v>
+        <v>0.0185</v>
       </c>
       <c r="G152" t="n">
         <v>35.788</v>
@@ -5313,7 +5313,7 @@
         <v>0.8643999999999999</v>
       </c>
       <c r="F153" t="n">
-        <v>1.9859</v>
+        <v>0.0141</v>
       </c>
       <c r="G153" t="n">
         <v>35.5437</v>
@@ -5345,7 +5345,7 @@
         <v>0.8629</v>
       </c>
       <c r="F154" t="n">
-        <v>1.9822</v>
+        <v>0.0178</v>
       </c>
       <c r="G154" t="n">
         <v>35.5035</v>
@@ -5377,7 +5377,7 @@
         <v>0.8817</v>
       </c>
       <c r="F155" t="n">
-        <v>1.9078</v>
+        <v>0.0922</v>
       </c>
       <c r="G155" t="n">
         <v>31.9896</v>
@@ -5409,7 +5409,7 @@
         <v>0.8911</v>
       </c>
       <c r="F156" t="n">
-        <v>1.9082</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G156" t="n">
         <v>32.0706</v>
@@ -5441,7 +5441,7 @@
         <v>0.8867</v>
       </c>
       <c r="F157" t="n">
-        <v>1.8988</v>
+        <v>0.1012</v>
       </c>
       <c r="G157" t="n">
         <v>32.4796</v>
@@ -5473,7 +5473,7 @@
         <v>0.8754999999999999</v>
       </c>
       <c r="F158" t="n">
-        <v>1.8904</v>
+        <v>0.1096</v>
       </c>
       <c r="G158" t="n">
         <v>35.0827</v>
@@ -5505,7 +5505,7 @@
         <v>0.8532</v>
       </c>
       <c r="F159" t="n">
-        <v>2.0545</v>
+        <v>-0.0545</v>
       </c>
       <c r="G159" t="n">
         <v>35.4186</v>
@@ -5537,7 +5537,7 @@
         <v>0.889</v>
       </c>
       <c r="F160" t="n">
-        <v>1.9798</v>
+        <v>0.0202</v>
       </c>
       <c r="G160" t="n">
         <v>33.0023</v>
@@ -5569,7 +5569,7 @@
         <v>0.8535</v>
       </c>
       <c r="F161" t="n">
-        <v>1.9762</v>
+        <v>0.0238</v>
       </c>
       <c r="G161" t="n">
         <v>35.5064</v>
@@ -5601,7 +5601,7 @@
         <v>0.8518</v>
       </c>
       <c r="F162" t="n">
-        <v>2.0449</v>
+        <v>-0.0449</v>
       </c>
       <c r="G162" t="n">
         <v>35.5736</v>
@@ -5633,7 +5633,7 @@
         <v>0.8961</v>
       </c>
       <c r="F163" t="n">
-        <v>1.9154</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="G163" t="n">
         <v>32.4985</v>
@@ -5665,7 +5665,7 @@
         <v>0.9137999999999999</v>
       </c>
       <c r="F164" t="n">
-        <v>1.8062</v>
+        <v>0.1938</v>
       </c>
       <c r="G164" t="n">
         <v>28.8625</v>
@@ -5697,7 +5697,7 @@
         <v>0.9265</v>
       </c>
       <c r="F165" t="n">
-        <v>1.9433</v>
+        <v>0.0567</v>
       </c>
       <c r="G165" t="n">
         <v>28.7581</v>
@@ -5729,7 +5729,7 @@
         <v>0.8058999999999999</v>
       </c>
       <c r="F166" t="n">
-        <v>2.1209</v>
+        <v>-0.1209</v>
       </c>
       <c r="G166" t="n">
         <v>41.6109</v>
@@ -5761,7 +5761,7 @@
         <v>0.9074</v>
       </c>
       <c r="F167" t="n">
-        <v>1.8617</v>
+        <v>0.1383</v>
       </c>
       <c r="G167" t="n">
         <v>30.3829</v>
@@ -5793,7 +5793,7 @@
         <v>0.9137999999999999</v>
       </c>
       <c r="F168" t="n">
-        <v>1.8126</v>
+        <v>0.1874</v>
       </c>
       <c r="G168" t="n">
         <v>28.9638</v>
@@ -5825,7 +5825,7 @@
         <v>0.945</v>
       </c>
       <c r="F169" t="n">
-        <v>1.9122</v>
+        <v>0.0878</v>
       </c>
       <c r="G169" t="n">
         <v>25.457</v>
@@ -5857,7 +5857,7 @@
         <v>0.8473000000000001</v>
       </c>
       <c r="F170" t="n">
-        <v>1.9126</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="G170" t="n">
         <v>37.8024</v>
@@ -5889,7 +5889,7 @@
         <v>0.9129</v>
       </c>
       <c r="F171" t="n">
-        <v>1.845</v>
+        <v>0.155</v>
       </c>
       <c r="G171" t="n">
         <v>29.6294</v>
@@ -5921,7 +5921,7 @@
         <v>0.9332</v>
       </c>
       <c r="F172" t="n">
-        <v>1.9419</v>
+        <v>0.0581</v>
       </c>
       <c r="G172" t="n">
         <v>28.8077</v>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/HR/dT3/RANDOMSEARCH_DETAILS_dT3.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/HR/dT3/RANDOMSEARCH_DETAILS_dT3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.8923</v>
+        <v>0.8925</v>
       </c>
       <c r="F35" t="n">
         <v>0.1503</v>
       </c>
       <c r="G35" t="n">
-        <v>32.7834</v>
+        <v>32.7759</v>
       </c>
       <c r="H35" t="n">
         <v>54.3178</v>
@@ -2609,11 +2609,11 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.8354</v>
+        <v>0.8877</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0288</v>
+        <v>0.0408</v>
       </c>
       <c r="G69" t="n">
-        <v>36.5972</v>
+        <v>34.7521</v>
       </c>
       <c r="H69" t="n">
-        <v>58.0726</v>
+        <v>57.7145</v>
       </c>
     </row>
     <row r="70">
@@ -2641,29 +2641,29 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8476</v>
+        <v>0.9368</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0297</v>
+        <v>0.0523</v>
       </c>
       <c r="G70" t="n">
-        <v>35.0963</v>
+        <v>27.3793</v>
       </c>
       <c r="H70" t="n">
-        <v>58.0457</v>
+        <v>57.365</v>
       </c>
     </row>
     <row r="71">
@@ -2673,29 +2673,29 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.8646</v>
+        <v>0.8721</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0464</v>
+        <v>0.1466</v>
       </c>
       <c r="G71" t="n">
-        <v>33.8664</v>
+        <v>34.7494</v>
       </c>
       <c r="H71" t="n">
-        <v>57.543</v>
+        <v>54.4374</v>
       </c>
     </row>
     <row r="72">
@@ -2705,29 +2705,29 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(2,3,21))</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.7889</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0237</v>
+        <v>0.1252</v>
       </c>
       <c r="G72" t="n">
-        <v>40.2994</v>
+        <v>34.8066</v>
       </c>
       <c r="H72" t="n">
-        <v>58.2249</v>
+        <v>55.1164</v>
       </c>
     </row>
     <row r="73">
@@ -2737,29 +2737,29 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.8569</v>
+        <v>0.8354</v>
       </c>
       <c r="F73" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0288</v>
       </c>
       <c r="G73" t="n">
-        <v>36.6617</v>
+        <v>36.5972</v>
       </c>
       <c r="H73" t="n">
-        <v>56.8553</v>
+        <v>58.0726</v>
       </c>
     </row>
     <row r="74">
@@ -2769,29 +2769,29 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.8635</v>
+        <v>0.8476</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0832</v>
+        <v>0.0297</v>
       </c>
       <c r="G74" t="n">
-        <v>34.2777</v>
+        <v>35.0963</v>
       </c>
       <c r="H74" t="n">
-        <v>56.4217</v>
+        <v>58.0457</v>
       </c>
     </row>
     <row r="75">
@@ -2801,29 +2801,29 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.8366</v>
+        <v>0.8646</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.0483</v>
+        <v>0.0464</v>
       </c>
       <c r="G75" t="n">
-        <v>37.1537</v>
+        <v>33.8664</v>
       </c>
       <c r="H75" t="n">
-        <v>60.3339</v>
+        <v>57.543</v>
       </c>
     </row>
     <row r="76">
@@ -2833,29 +2833,29 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8366</v>
+        <v>0.7889</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0483</v>
+        <v>0.0237</v>
       </c>
       <c r="G76" t="n">
-        <v>37.1537</v>
+        <v>40.2994</v>
       </c>
       <c r="H76" t="n">
-        <v>60.3339</v>
+        <v>58.2249</v>
       </c>
     </row>
     <row r="77">
@@ -2865,29 +2865,29 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8166</v>
+        <v>0.8569</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.0752</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>41.0568</v>
+        <v>36.6617</v>
       </c>
       <c r="H77" t="n">
-        <v>61.1047</v>
+        <v>56.8553</v>
       </c>
     </row>
     <row r="78">
@@ -2897,29 +2897,29 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8105</v>
+        <v>0.8635</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.0832</v>
       </c>
       <c r="G78" t="n">
-        <v>41.4008</v>
+        <v>34.2777</v>
       </c>
       <c r="H78" t="n">
-        <v>61.1064</v>
+        <v>56.4217</v>
       </c>
     </row>
     <row r="79">
@@ -2929,29 +2929,29 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8094</v>
+        <v>0.8366</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.0809</v>
+        <v>-0.0483</v>
       </c>
       <c r="G79" t="n">
-        <v>41.4587</v>
+        <v>37.1537</v>
       </c>
       <c r="H79" t="n">
-        <v>61.2655</v>
+        <v>60.3339</v>
       </c>
     </row>
     <row r="80">
@@ -2961,29 +2961,29 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8114</v>
+        <v>0.8366</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.0737</v>
+        <v>-0.0483</v>
       </c>
       <c r="G80" t="n">
-        <v>41.3378</v>
+        <v>37.1537</v>
       </c>
       <c r="H80" t="n">
-        <v>61.0606</v>
+        <v>60.3339</v>
       </c>
     </row>
     <row r="81">
@@ -2993,29 +2993,29 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.88</v>
+        <v>0.8166</v>
       </c>
       <c r="F81" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.0752</v>
       </c>
       <c r="G81" t="n">
-        <v>32.9225</v>
+        <v>41.0568</v>
       </c>
       <c r="H81" t="n">
-        <v>56.6032</v>
+        <v>61.1047</v>
       </c>
     </row>
     <row r="82">
@@ -3025,29 +3025,29 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.976</v>
+        <v>0.8105</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0633</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>21.8957</v>
+        <v>41.4008</v>
       </c>
       <c r="H82" t="n">
-        <v>57.0335</v>
+        <v>61.1064</v>
       </c>
     </row>
     <row r="83">
@@ -3057,29 +3057,29 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9066</v>
+        <v>0.8094</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.0576</v>
+        <v>-0.0809</v>
       </c>
       <c r="G83" t="n">
-        <v>30.6794</v>
+        <v>41.4587</v>
       </c>
       <c r="H83" t="n">
-        <v>60.6026</v>
+        <v>61.2655</v>
       </c>
     </row>
     <row r="84">
@@ -3089,29 +3089,29 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.8114</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.0532</v>
+        <v>-0.0737</v>
       </c>
       <c r="G84" t="n">
-        <v>30.8357</v>
+        <v>41.3378</v>
       </c>
       <c r="H84" t="n">
-        <v>60.4755</v>
+        <v>61.0606</v>
       </c>
     </row>
     <row r="85">
@@ -3121,29 +3121,29 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.835</v>
+        <v>0.88</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.0576</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>37.2952</v>
+        <v>32.9225</v>
       </c>
       <c r="H85" t="n">
-        <v>60.6007</v>
+        <v>56.6032</v>
       </c>
     </row>
     <row r="86">
@@ -3153,29 +3153,29 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9051</v>
+        <v>0.976</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1597</v>
+        <v>0.0633</v>
       </c>
       <c r="G86" t="n">
-        <v>30.382</v>
+        <v>21.8957</v>
       </c>
       <c r="H86" t="n">
-        <v>54.0168</v>
+        <v>57.0335</v>
       </c>
     </row>
     <row r="87">
@@ -3185,29 +3185,29 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.8988</v>
+        <v>0.9066</v>
       </c>
       <c r="F87" t="n">
-        <v>0.138</v>
+        <v>-0.0576</v>
       </c>
       <c r="G87" t="n">
-        <v>33.03</v>
+        <v>30.6794</v>
       </c>
       <c r="H87" t="n">
-        <v>54.7118</v>
+        <v>60.6026</v>
       </c>
     </row>
     <row r="88">
@@ -3217,29 +3217,29 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.8971</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="F88" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.0532</v>
       </c>
       <c r="G88" t="n">
-        <v>31.237</v>
+        <v>30.8357</v>
       </c>
       <c r="H88" t="n">
-        <v>55.9321</v>
+        <v>60.4755</v>
       </c>
     </row>
     <row r="89">
@@ -3249,29 +3249,29 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.8904</v>
+        <v>0.835</v>
       </c>
       <c r="F89" t="n">
-        <v>0.08790000000000001</v>
+        <v>-0.0576</v>
       </c>
       <c r="G89" t="n">
-        <v>33.9542</v>
+        <v>37.2952</v>
       </c>
       <c r="H89" t="n">
-        <v>56.2784</v>
+        <v>60.6007</v>
       </c>
     </row>
     <row r="90">
@@ -3281,11 +3281,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3294,16 +3294,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9095</v>
+        <v>0.9051</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1661</v>
+        <v>0.1597</v>
       </c>
       <c r="G90" t="n">
-        <v>29.2561</v>
+        <v>30.382</v>
       </c>
       <c r="H90" t="n">
-        <v>53.813</v>
+        <v>54.0168</v>
       </c>
     </row>
     <row r="91">
@@ -3313,29 +3313,29 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9282</v>
+        <v>0.8988</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1536</v>
+        <v>0.138</v>
       </c>
       <c r="G91" t="n">
-        <v>28.1467</v>
+        <v>33.03</v>
       </c>
       <c r="H91" t="n">
-        <v>54.213</v>
+        <v>54.7118</v>
       </c>
     </row>
     <row r="92">
@@ -3345,11 +3345,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3377,29 +3377,29 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9282</v>
+        <v>0.8904</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1536</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>28.1467</v>
+        <v>33.9542</v>
       </c>
       <c r="H93" t="n">
-        <v>54.213</v>
+        <v>56.2784</v>
       </c>
     </row>
     <row r="94">
@@ -3409,29 +3409,29 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9669</v>
+        <v>0.9095</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0507</v>
+        <v>0.1661</v>
       </c>
       <c r="G94" t="n">
-        <v>21.4985</v>
+        <v>29.2561</v>
       </c>
       <c r="H94" t="n">
-        <v>57.4142</v>
+        <v>53.813</v>
       </c>
     </row>
     <row r="95">
@@ -3441,29 +3441,29 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7904</v>
+        <v>0.9282</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.1358</v>
+        <v>0.1536</v>
       </c>
       <c r="G95" t="n">
-        <v>42.6939</v>
+        <v>28.1467</v>
       </c>
       <c r="H95" t="n">
-        <v>62.8023</v>
+        <v>54.213</v>
       </c>
     </row>
     <row r="96">
@@ -3473,29 +3473,29 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8721</v>
+        <v>0.8971</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0607</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G96" t="n">
-        <v>35.2133</v>
+        <v>31.237</v>
       </c>
       <c r="H96" t="n">
-        <v>57.1113</v>
+        <v>55.9321</v>
       </c>
     </row>
     <row r="97">
@@ -3505,29 +3505,29 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.917</v>
+        <v>0.9282</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0623</v>
+        <v>0.1536</v>
       </c>
       <c r="G97" t="n">
-        <v>28.2502</v>
+        <v>28.1467</v>
       </c>
       <c r="H97" t="n">
-        <v>57.0635</v>
+        <v>54.213</v>
       </c>
     </row>
     <row r="98">
@@ -3537,29 +3537,29 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9029</v>
+        <v>0.9669</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1743</v>
+        <v>0.0507</v>
       </c>
       <c r="G98" t="n">
-        <v>29.9956</v>
+        <v>21.4985</v>
       </c>
       <c r="H98" t="n">
-        <v>53.5479</v>
+        <v>57.4142</v>
       </c>
     </row>
     <row r="99">
@@ -3569,29 +3569,29 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.7904</v>
       </c>
       <c r="F99" t="n">
-        <v>0.094</v>
+        <v>-0.1358</v>
       </c>
       <c r="G99" t="n">
-        <v>33.7179</v>
+        <v>42.6939</v>
       </c>
       <c r="H99" t="n">
-        <v>56.0885</v>
+        <v>62.8023</v>
       </c>
     </row>
     <row r="100">
@@ -3601,11 +3601,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3614,16 +3614,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9304</v>
+        <v>0.8721</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1103</v>
+        <v>0.0607</v>
       </c>
       <c r="G100" t="n">
-        <v>30.1391</v>
+        <v>35.2133</v>
       </c>
       <c r="H100" t="n">
-        <v>55.5828</v>
+        <v>57.1113</v>
       </c>
     </row>
     <row r="101">
@@ -3633,29 +3633,29 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9274</v>
+        <v>0.917</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1082</v>
+        <v>0.0623</v>
       </c>
       <c r="G101" t="n">
-        <v>28.2514</v>
+        <v>28.2502</v>
       </c>
       <c r="H101" t="n">
-        <v>55.6478</v>
+        <v>57.0635</v>
       </c>
     </row>
     <row r="102">
@@ -3665,29 +3665,29 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.8894</v>
+        <v>0.9029</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0776</v>
+        <v>0.1743</v>
       </c>
       <c r="G102" t="n">
-        <v>33.4419</v>
+        <v>29.9956</v>
       </c>
       <c r="H102" t="n">
-        <v>56.596</v>
+        <v>53.5479</v>
       </c>
     </row>
     <row r="103">
@@ -3697,29 +3697,29 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9014</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1528</v>
+        <v>0.094</v>
       </c>
       <c r="G103" t="n">
-        <v>30.3509</v>
+        <v>33.7179</v>
       </c>
       <c r="H103" t="n">
-        <v>54.2395</v>
+        <v>56.0885</v>
       </c>
     </row>
     <row r="104">
@@ -3729,29 +3729,29 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.8951</v>
+        <v>0.9304</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1315</v>
+        <v>0.1103</v>
       </c>
       <c r="G104" t="n">
-        <v>33.1695</v>
+        <v>30.1391</v>
       </c>
       <c r="H104" t="n">
-        <v>54.9174</v>
+        <v>55.5828</v>
       </c>
     </row>
     <row r="105">
@@ -3761,29 +3761,29 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9109</v>
+        <v>0.9274</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1333</v>
+        <v>0.1082</v>
       </c>
       <c r="G105" t="n">
-        <v>30.2069</v>
+        <v>28.2514</v>
       </c>
       <c r="H105" t="n">
-        <v>54.8595</v>
+        <v>55.6478</v>
       </c>
     </row>
     <row r="106">
@@ -3793,29 +3793,29 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9731</v>
+        <v>0.8894</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1041</v>
+        <v>0.0776</v>
       </c>
       <c r="G106" t="n">
-        <v>21.1915</v>
+        <v>33.4419</v>
       </c>
       <c r="H106" t="n">
-        <v>55.7771</v>
+        <v>56.596</v>
       </c>
     </row>
     <row r="107">
@@ -3825,29 +3825,29 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9716</v>
+        <v>0.9014</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1041</v>
+        <v>0.1528</v>
       </c>
       <c r="G107" t="n">
-        <v>21.1323</v>
+        <v>30.3509</v>
       </c>
       <c r="H107" t="n">
-        <v>55.7752</v>
+        <v>54.2395</v>
       </c>
     </row>
     <row r="108">
@@ -3857,29 +3857,29 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.893</v>
+        <v>0.8951</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1344</v>
+        <v>0.1315</v>
       </c>
       <c r="G108" t="n">
-        <v>32.3814</v>
+        <v>33.1695</v>
       </c>
       <c r="H108" t="n">
-        <v>54.8263</v>
+        <v>54.9174</v>
       </c>
     </row>
     <row r="109">
@@ -3889,29 +3889,29 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9087</v>
+        <v>0.9109</v>
       </c>
       <c r="F109" t="n">
-        <v>0.1708</v>
+        <v>0.1333</v>
       </c>
       <c r="G109" t="n">
-        <v>29.3713</v>
+        <v>30.2069</v>
       </c>
       <c r="H109" t="n">
-        <v>53.6593</v>
+        <v>54.8595</v>
       </c>
     </row>
     <row r="110">
@@ -3921,29 +3921,29 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9039</v>
+        <v>0.9731</v>
       </c>
       <c r="F110" t="n">
-        <v>0.1512</v>
+        <v>0.1041</v>
       </c>
       <c r="G110" t="n">
-        <v>30.3073</v>
+        <v>21.1915</v>
       </c>
       <c r="H110" t="n">
-        <v>54.2913</v>
+        <v>55.7771</v>
       </c>
     </row>
     <row r="111">
@@ -3953,29 +3953,29 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.8772</v>
+        <v>0.9716</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1127</v>
+        <v>0.1041</v>
       </c>
       <c r="G111" t="n">
-        <v>33.743</v>
+        <v>21.1323</v>
       </c>
       <c r="H111" t="n">
-        <v>55.5075</v>
+        <v>55.7752</v>
       </c>
     </row>
     <row r="112">
@@ -3985,11 +3985,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.8923</v>
+        <v>0.893</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1387</v>
+        <v>0.1344</v>
       </c>
       <c r="G112" t="n">
-        <v>32.4659</v>
+        <v>32.3814</v>
       </c>
       <c r="H112" t="n">
-        <v>54.688</v>
+        <v>54.8263</v>
       </c>
     </row>
     <row r="113">
@@ -4017,11 +4017,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4030,16 +4030,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9095</v>
+        <v>0.9087</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1726</v>
+        <v>0.1708</v>
       </c>
       <c r="G113" t="n">
-        <v>29.3003</v>
+        <v>29.3713</v>
       </c>
       <c r="H113" t="n">
-        <v>53.6028</v>
+        <v>53.6593</v>
       </c>
     </row>
     <row r="114">
@@ -4049,11 +4049,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4062,16 +4062,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9034</v>
+        <v>0.9035</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1421</v>
+        <v>0.1512</v>
       </c>
       <c r="G114" t="n">
-        <v>30.386</v>
+        <v>30.3506</v>
       </c>
       <c r="H114" t="n">
-        <v>54.5797</v>
+        <v>54.2913</v>
       </c>
     </row>
     <row r="115">
@@ -4081,11 +4081,11 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4094,16 +4094,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.8803</v>
+        <v>0.8772</v>
       </c>
       <c r="F115" t="n">
-        <v>0.1095</v>
+        <v>0.1127</v>
       </c>
       <c r="G115" t="n">
-        <v>33.5836</v>
+        <v>33.743</v>
       </c>
       <c r="H115" t="n">
-        <v>55.6074</v>
+        <v>55.5075</v>
       </c>
     </row>
     <row r="116">
@@ -4113,29 +4113,29 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8842</v>
+        <v>0.8923</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0901</v>
+        <v>0.1387</v>
       </c>
       <c r="G116" t="n">
-        <v>32.3853</v>
+        <v>32.4659</v>
       </c>
       <c r="H116" t="n">
-        <v>56.211</v>
+        <v>54.688</v>
       </c>
     </row>
     <row r="117">
@@ -4145,29 +4145,29 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8774</v>
+        <v>0.9095</v>
       </c>
       <c r="F117" t="n">
-        <v>0.0273</v>
+        <v>0.1726</v>
       </c>
       <c r="G117" t="n">
-        <v>33.6299</v>
+        <v>29.3003</v>
       </c>
       <c r="H117" t="n">
-        <v>58.1183</v>
+        <v>53.6028</v>
       </c>
     </row>
     <row r="118">
@@ -4177,29 +4177,29 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9109</v>
+        <v>0.9034</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1333</v>
+        <v>0.1421</v>
       </c>
       <c r="G118" t="n">
-        <v>30.2069</v>
+        <v>30.386</v>
       </c>
       <c r="H118" t="n">
-        <v>54.8595</v>
+        <v>54.5797</v>
       </c>
     </row>
     <row r="119">
@@ -4209,29 +4209,29 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9095</v>
+        <v>0.8803</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1726</v>
+        <v>0.1095</v>
       </c>
       <c r="G119" t="n">
-        <v>29.3003</v>
+        <v>33.5836</v>
       </c>
       <c r="H119" t="n">
-        <v>53.6028</v>
+        <v>55.6074</v>
       </c>
     </row>
     <row r="120">
@@ -4241,11 +4241,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4254,16 +4254,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8611</v>
+        <v>0.8842</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.0192</v>
+        <v>0.0901</v>
       </c>
       <c r="G120" t="n">
-        <v>35.968</v>
+        <v>32.3853</v>
       </c>
       <c r="H120" t="n">
-        <v>59.4919</v>
+        <v>56.211</v>
       </c>
     </row>
     <row r="121">
@@ -4273,11 +4273,11 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4286,16 +4286,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8611</v>
+        <v>0.8774</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.0192</v>
+        <v>0.0273</v>
       </c>
       <c r="G121" t="n">
-        <v>35.968</v>
+        <v>33.6299</v>
       </c>
       <c r="H121" t="n">
-        <v>59.4919</v>
+        <v>58.1183</v>
       </c>
     </row>
     <row r="122">
@@ -4305,29 +4305,29 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.8837</v>
+        <v>0.9109</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0621</v>
+        <v>0.1333</v>
       </c>
       <c r="G122" t="n">
-        <v>34.4531</v>
+        <v>30.2069</v>
       </c>
       <c r="H122" t="n">
-        <v>57.0691</v>
+        <v>54.8595</v>
       </c>
     </row>
     <row r="123">
@@ -4337,11 +4337,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4350,16 +4350,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9096</v>
+        <v>0.9095</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1723</v>
+        <v>0.1726</v>
       </c>
       <c r="G123" t="n">
-        <v>29.2973</v>
+        <v>29.3003</v>
       </c>
       <c r="H123" t="n">
-        <v>53.6109</v>
+        <v>53.6028</v>
       </c>
     </row>
     <row r="124">
@@ -4369,29 +4369,29 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.8925</v>
+        <v>0.8611</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1285</v>
+        <v>-0.0192</v>
       </c>
       <c r="G124" t="n">
-        <v>33.1135</v>
+        <v>35.968</v>
       </c>
       <c r="H124" t="n">
-        <v>55.0112</v>
+        <v>59.4919</v>
       </c>
     </row>
     <row r="125">
@@ -4401,29 +4401,29 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9265</v>
+        <v>0.8611</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0567</v>
+        <v>-0.0192</v>
       </c>
       <c r="G125" t="n">
-        <v>28.7581</v>
+        <v>35.968</v>
       </c>
       <c r="H125" t="n">
-        <v>57.2323</v>
+        <v>59.4919</v>
       </c>
     </row>
     <row r="126">
@@ -4433,29 +4433,29 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8678</v>
+        <v>0.8837</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.0881</v>
+        <v>0.0621</v>
       </c>
       <c r="G126" t="n">
-        <v>36.0423</v>
+        <v>34.4531</v>
       </c>
       <c r="H126" t="n">
-        <v>61.4689</v>
+        <v>57.0691</v>
       </c>
     </row>
     <row r="127">
@@ -4465,29 +4465,29 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8561</v>
+        <v>0.9096</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0162</v>
+        <v>0.1723</v>
       </c>
       <c r="G127" t="n">
-        <v>36.0802</v>
+        <v>29.2973</v>
       </c>
       <c r="H127" t="n">
-        <v>58.4472</v>
+        <v>53.6109</v>
       </c>
     </row>
     <row r="128">
@@ -4497,29 +4497,29 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.8631</v>
+        <v>0.8925</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.08690000000000001</v>
+        <v>0.1285</v>
       </c>
       <c r="G128" t="n">
-        <v>36.5375</v>
+        <v>33.1135</v>
       </c>
       <c r="H128" t="n">
-        <v>61.4356</v>
+        <v>55.0112</v>
       </c>
     </row>
     <row r="129">
@@ -4529,29 +4529,29 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1))</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8565</v>
+        <v>0.9265</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.0994</v>
+        <v>0.0567</v>
       </c>
       <c r="G129" t="n">
-        <v>37.1822</v>
+        <v>28.7581</v>
       </c>
       <c r="H129" t="n">
-        <v>61.786</v>
+        <v>57.2323</v>
       </c>
     </row>
     <row r="130">
@@ -4561,11 +4561,11 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv','')</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4574,16 +4574,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.8559</v>
+        <v>0.8678</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.0906</v>
+        <v>-0.0881</v>
       </c>
       <c r="G130" t="n">
-        <v>37.1213</v>
+        <v>36.0423</v>
       </c>
       <c r="H130" t="n">
-        <v>61.5385</v>
+        <v>61.4689</v>
       </c>
     </row>
     <row r="131">
@@ -4593,29 +4593,29 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv','')</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9293</v>
+        <v>0.8561</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.0162</v>
       </c>
       <c r="G131" t="n">
-        <v>29.6303</v>
+        <v>36.0802</v>
       </c>
       <c r="H131" t="n">
-        <v>61.396</v>
+        <v>58.4472</v>
       </c>
     </row>
     <row r="132">
@@ -4625,29 +4625,29 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9193</v>
+        <v>0.8631</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="G132" t="n">
-        <v>32.3592</v>
+        <v>36.5375</v>
       </c>
       <c r="H132" t="n">
-        <v>61.6441</v>
+        <v>61.4356</v>
       </c>
     </row>
     <row r="133">
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8572</v>
+        <v>0.8565</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.0882</v>
+        <v>-0.0994</v>
       </c>
       <c r="G133" t="n">
-        <v>36.8122</v>
+        <v>37.1822</v>
       </c>
       <c r="H133" t="n">
-        <v>61.473</v>
+        <v>61.786</v>
       </c>
     </row>
     <row r="134">
@@ -4689,29 +4689,29 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.8612</v>
+        <v>0.8559</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.0963</v>
+        <v>-0.0906</v>
       </c>
       <c r="G134" t="n">
-        <v>36.5822</v>
+        <v>37.1213</v>
       </c>
       <c r="H134" t="n">
-        <v>61.7003</v>
+        <v>61.5385</v>
       </c>
     </row>
     <row r="135">
@@ -4721,29 +4721,29 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.8596</v>
+        <v>0.9293</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.09229999999999999</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>36.8706</v>
+        <v>29.6303</v>
       </c>
       <c r="H135" t="n">
-        <v>61.5886</v>
+        <v>61.396</v>
       </c>
     </row>
     <row r="136">
@@ -4753,29 +4753,29 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9316</v>
+        <v>0.9193</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.0866</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="G136" t="n">
-        <v>29.4965</v>
+        <v>32.3592</v>
       </c>
       <c r="H136" t="n">
-        <v>61.4252</v>
+        <v>61.6441</v>
       </c>
     </row>
     <row r="137">
@@ -4785,29 +4785,29 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,2,11))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9769</v>
+        <v>0.8572</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1145</v>
+        <v>-0.0882</v>
       </c>
       <c r="G137" t="n">
-        <v>21.0941</v>
+        <v>36.8122</v>
       </c>
       <c r="H137" t="n">
-        <v>55.4506</v>
+        <v>61.473</v>
       </c>
     </row>
     <row r="138">
@@ -4817,11 +4817,11 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4830,16 +4830,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9167</v>
+        <v>0.8612</v>
       </c>
       <c r="F138" t="n">
-        <v>0.1685</v>
+        <v>-0.0963</v>
       </c>
       <c r="G138" t="n">
-        <v>30.1262</v>
+        <v>36.5822</v>
       </c>
       <c r="H138" t="n">
-        <v>53.7358</v>
+        <v>61.7003</v>
       </c>
     </row>
     <row r="139">
@@ -4849,29 +4849,29 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.8834</v>
+        <v>0.8596</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1037</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>34.0618</v>
+        <v>36.8706</v>
       </c>
       <c r="H139" t="n">
-        <v>55.789</v>
+        <v>61.5886</v>
       </c>
     </row>
     <row r="140">
@@ -4881,29 +4881,29 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0,3,31))</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9136</v>
+        <v>0.9316</v>
       </c>
       <c r="F140" t="n">
-        <v>0.194</v>
+        <v>-0.0866</v>
       </c>
       <c r="G140" t="n">
-        <v>28.8848</v>
+        <v>29.4965</v>
       </c>
       <c r="H140" t="n">
-        <v>52.9029</v>
+        <v>61.4252</v>
       </c>
     </row>
     <row r="141">
@@ -4913,29 +4913,29 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,2,11))</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9769</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1201</v>
+        <v>0.1145</v>
       </c>
       <c r="G141" t="n">
-        <v>30.5956</v>
+        <v>21.0941</v>
       </c>
       <c r="H141" t="n">
-        <v>55.2772</v>
+        <v>55.4506</v>
       </c>
     </row>
     <row r="142">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -4977,29 +4977,29 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.8885</v>
+        <v>0.8834</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1018</v>
+        <v>0.1037</v>
       </c>
       <c r="G143" t="n">
-        <v>32.0823</v>
+        <v>34.0618</v>
       </c>
       <c r="H143" t="n">
-        <v>55.8487</v>
+        <v>55.789</v>
       </c>
     </row>
     <row r="144">
@@ -5009,29 +5009,29 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.8797</v>
+        <v>0.9136</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1084</v>
+        <v>0.194</v>
       </c>
       <c r="G144" t="n">
-        <v>34.1064</v>
+        <v>28.8848</v>
       </c>
       <c r="H144" t="n">
-        <v>55.6438</v>
+        <v>52.9029</v>
       </c>
     </row>
     <row r="145">
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8611</v>
+        <v>0.9167</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0131</v>
+        <v>0.1685</v>
       </c>
       <c r="G146" t="n">
-        <v>35.6587</v>
+        <v>30.1262</v>
       </c>
       <c r="H146" t="n">
-        <v>58.5413</v>
+        <v>53.7358</v>
       </c>
     </row>
     <row r="147">
@@ -5105,29 +5105,29 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,25))</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.854</v>
+        <v>0.8885</v>
       </c>
       <c r="F147" t="n">
-        <v>0.003</v>
+        <v>0.1018</v>
       </c>
       <c r="G147" t="n">
-        <v>36.119</v>
+        <v>32.0823</v>
       </c>
       <c r="H147" t="n">
-        <v>58.8399</v>
+        <v>55.8487</v>
       </c>
     </row>
     <row r="148">
@@ -5137,29 +5137,29 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,31))</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8589</v>
+        <v>0.8797</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.0002</v>
+        <v>0.1084</v>
       </c>
       <c r="G148" t="n">
-        <v>35.8903</v>
+        <v>34.1064</v>
       </c>
       <c r="H148" t="n">
-        <v>58.9326</v>
+        <v>55.6438</v>
       </c>
     </row>
     <row r="149">
@@ -5169,29 +5169,29 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.861</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.0035</v>
+        <v>0.1201</v>
       </c>
       <c r="G149" t="n">
-        <v>35.8015</v>
+        <v>30.5956</v>
       </c>
       <c r="H149" t="n">
-        <v>59.0313</v>
+        <v>55.2772</v>
       </c>
     </row>
     <row r="150">
@@ -5201,29 +5201,29 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8588</v>
+        <v>0.8611</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0161</v>
+        <v>0.0131</v>
       </c>
       <c r="G150" t="n">
-        <v>35.8139</v>
+        <v>35.6587</v>
       </c>
       <c r="H150" t="n">
-        <v>58.4524</v>
+        <v>58.5413</v>
       </c>
     </row>
     <row r="151">
@@ -5233,11 +5233,11 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5246,16 +5246,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8607</v>
+        <v>0.854</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0138</v>
+        <v>0.003</v>
       </c>
       <c r="G151" t="n">
-        <v>35.7174</v>
+        <v>36.1187</v>
       </c>
       <c r="H151" t="n">
-        <v>58.5201</v>
+        <v>58.8399</v>
       </c>
     </row>
     <row r="152">
@@ -5265,29 +5265,29 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8609</v>
+        <v>0.8589</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0185</v>
+        <v>-0.0002</v>
       </c>
       <c r="G152" t="n">
-        <v>35.788</v>
+        <v>35.8903</v>
       </c>
       <c r="H152" t="n">
-        <v>58.3806</v>
+        <v>58.9326</v>
       </c>
     </row>
     <row r="153">
@@ -5297,29 +5297,29 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.861</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0141</v>
+        <v>-0.0035</v>
       </c>
       <c r="G153" t="n">
-        <v>35.5437</v>
+        <v>35.8015</v>
       </c>
       <c r="H153" t="n">
-        <v>58.511</v>
+        <v>59.0313</v>
       </c>
     </row>
     <row r="154">
@@ -5329,11 +5329,11 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5342,16 +5342,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8629</v>
+        <v>0.8588</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0178</v>
+        <v>0.0161</v>
       </c>
       <c r="G154" t="n">
-        <v>35.5035</v>
+        <v>35.8139</v>
       </c>
       <c r="H154" t="n">
-        <v>58.4002</v>
+        <v>58.4524</v>
       </c>
     </row>
     <row r="155">
@@ -5361,11 +5361,11 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5374,16 +5374,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8817</v>
+        <v>0.8607</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0922</v>
+        <v>0.0138</v>
       </c>
       <c r="G155" t="n">
-        <v>31.9896</v>
+        <v>35.717</v>
       </c>
       <c r="H155" t="n">
-        <v>56.1471</v>
+        <v>58.5201</v>
       </c>
     </row>
     <row r="156">
@@ -5393,11 +5393,11 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5406,16 +5406,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.8911</v>
+        <v>0.8609</v>
       </c>
       <c r="F156" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0185</v>
       </c>
       <c r="G156" t="n">
-        <v>32.0706</v>
+        <v>35.788</v>
       </c>
       <c r="H156" t="n">
-        <v>56.1567</v>
+        <v>58.3806</v>
       </c>
     </row>
     <row r="157">
@@ -5425,29 +5425,29 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8867</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>0.1012</v>
+        <v>0.0141</v>
       </c>
       <c r="G157" t="n">
-        <v>32.4796</v>
+        <v>35.5437</v>
       </c>
       <c r="H157" t="n">
-        <v>55.8665</v>
+        <v>58.511</v>
       </c>
     </row>
     <row r="158">
@@ -5457,29 +5457,29 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8629</v>
       </c>
       <c r="F158" t="n">
-        <v>0.1096</v>
+        <v>0.0178</v>
       </c>
       <c r="G158" t="n">
-        <v>35.0827</v>
+        <v>35.5035</v>
       </c>
       <c r="H158" t="n">
-        <v>55.6053</v>
+        <v>58.4002</v>
       </c>
     </row>
     <row r="159">
@@ -5489,29 +5489,29 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8532</v>
+        <v>0.8817</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.0545</v>
+        <v>0.0922</v>
       </c>
       <c r="G159" t="n">
-        <v>35.4186</v>
+        <v>31.9896</v>
       </c>
       <c r="H159" t="n">
-        <v>60.5127</v>
+        <v>56.1471</v>
       </c>
     </row>
     <row r="160">
@@ -5521,29 +5521,29 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,25))</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.889</v>
+        <v>0.8911</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0202</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>33.0023</v>
+        <v>32.0706</v>
       </c>
       <c r="H160" t="n">
-        <v>58.3299</v>
+        <v>56.1567</v>
       </c>
     </row>
     <row r="161">
@@ -5553,29 +5553,29 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8535</v>
+        <v>0.8867</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0238</v>
+        <v>0.1012</v>
       </c>
       <c r="G161" t="n">
-        <v>35.5064</v>
+        <v>32.4796</v>
       </c>
       <c r="H161" t="n">
-        <v>58.2211</v>
+        <v>55.8665</v>
       </c>
     </row>
     <row r="162">
@@ -5585,29 +5585,29 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,21))</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.8518</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.0449</v>
+        <v>0.1096</v>
       </c>
       <c r="G162" t="n">
-        <v>35.5736</v>
+        <v>35.0827</v>
       </c>
       <c r="H162" t="n">
-        <v>60.2354</v>
+        <v>55.6053</v>
       </c>
     </row>
     <row r="163">
@@ -5617,29 +5617,29 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.8961</v>
+        <v>0.8532</v>
       </c>
       <c r="F163" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0545</v>
       </c>
       <c r="G163" t="n">
-        <v>32.4985</v>
+        <v>35.4186</v>
       </c>
       <c r="H163" t="n">
-        <v>56.3811</v>
+        <v>60.5127</v>
       </c>
     </row>
     <row r="164">
@@ -5649,29 +5649,29 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1938</v>
+        <v>0.0202</v>
       </c>
       <c r="G164" t="n">
-        <v>28.8625</v>
+        <v>33.0023</v>
       </c>
       <c r="H164" t="n">
-        <v>52.9097</v>
+        <v>58.3299</v>
       </c>
     </row>
     <row r="165">
@@ -5681,29 +5681,29 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc','')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9265</v>
+        <v>0.8535</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0567</v>
+        <v>0.0238</v>
       </c>
       <c r="G165" t="n">
-        <v>28.7581</v>
+        <v>35.5064</v>
       </c>
       <c r="H165" t="n">
-        <v>57.2323</v>
+        <v>58.2211</v>
       </c>
     </row>
     <row r="166">
@@ -5713,29 +5713,29 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('msc','')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.8518</v>
       </c>
       <c r="F166" t="n">
-        <v>-0.1209</v>
+        <v>-0.0449</v>
       </c>
       <c r="G166" t="n">
-        <v>41.6109</v>
+        <v>35.5736</v>
       </c>
       <c r="H166" t="n">
-        <v>62.3896</v>
+        <v>60.2354</v>
       </c>
     </row>
     <row r="167">
@@ -5745,29 +5745,29 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9074</v>
+        <v>0.8961</v>
       </c>
       <c r="F167" t="n">
-        <v>0.1383</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="G167" t="n">
-        <v>30.3829</v>
+        <v>32.4985</v>
       </c>
       <c r="H167" t="n">
-        <v>54.7004</v>
+        <v>56.3811</v>
       </c>
     </row>
     <row r="168">
@@ -5777,11 +5777,11 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5793,13 +5793,13 @@
         <v>0.9137999999999999</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1874</v>
+        <v>0.1938</v>
       </c>
       <c r="G168" t="n">
-        <v>28.9638</v>
+        <v>28.8625</v>
       </c>
       <c r="H168" t="n">
-        <v>53.1201</v>
+        <v>52.9097</v>
       </c>
     </row>
     <row r="169">
@@ -5809,29 +5809,29 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.945</v>
+        <v>0.9265</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0878</v>
+        <v>0.0567</v>
       </c>
       <c r="G169" t="n">
-        <v>25.457</v>
+        <v>28.7581</v>
       </c>
       <c r="H169" t="n">
-        <v>56.2814</v>
+        <v>57.2323</v>
       </c>
     </row>
     <row r="170">
@@ -5841,29 +5841,29 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="F170" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.1209</v>
       </c>
       <c r="G170" t="n">
-        <v>37.8024</v>
+        <v>41.6109</v>
       </c>
       <c r="H170" t="n">
-        <v>56.2933</v>
+        <v>62.3896</v>
       </c>
     </row>
     <row r="171">
@@ -5873,11 +5873,11 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5886,16 +5886,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9129</v>
+        <v>0.9074</v>
       </c>
       <c r="F171" t="n">
-        <v>0.155</v>
+        <v>0.1383</v>
       </c>
       <c r="G171" t="n">
-        <v>29.6294</v>
+        <v>30.3829</v>
       </c>
       <c r="H171" t="n">
-        <v>54.1693</v>
+        <v>54.7004</v>
       </c>
     </row>
     <row r="172">
@@ -5905,28 +5905,156 @@
         </is>
       </c>
       <c r="B172" t="n">
+        <v>171</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.9137999999999999</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="G172" t="n">
+        <v>28.9638</v>
+      </c>
+      <c r="H172" t="n">
+        <v>53.1201</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>172</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.0878</v>
+      </c>
+      <c r="G173" t="n">
+        <v>25.457</v>
+      </c>
+      <c r="H173" t="n">
+        <v>56.2814</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>173</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0.8473000000000001</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="G174" t="n">
+        <v>37.8024</v>
+      </c>
+      <c r="H174" t="n">
+        <v>56.2933</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>174</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="G175" t="n">
+        <v>29.6294</v>
+      </c>
+      <c r="H175" t="n">
+        <v>54.1693</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>dT3</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
         <v>175</v>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('sder',c(1,3,31)), list('snv','')</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
-      <c r="E172" t="n">
+      <c r="E176" t="n">
         <v>0.9332</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F176" t="n">
         <v>0.0581</v>
       </c>
-      <c r="G172" t="n">
+      <c r="G176" t="n">
         <v>28.8077</v>
       </c>
-      <c r="H172" t="n">
+      <c r="H176" t="n">
         <v>57.1891</v>
       </c>
     </row>
